--- a/artfynd/A 39937-2024 artfynd.xlsx
+++ b/artfynd/A 39937-2024 artfynd.xlsx
@@ -1245,10 +1245,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121242466</v>
+        <v>121240324</v>
       </c>
       <c r="B6" t="n">
-        <v>90705</v>
+        <v>79715</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1257,40 +1257,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1300,10 +1292,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473518</v>
+        <v>473527</v>
       </c>
       <c r="R6" t="n">
-        <v>7045959</v>
+        <v>7046057</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1338,11 +1330,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1360,32 +1347,32 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>En smal död gran som är knäckt vid basen.</t>
+          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1403,10 +1390,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121238339</v>
+        <v>121246722</v>
       </c>
       <c r="B7" t="n">
-        <v>91370</v>
+        <v>79714</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1419,37 +1406,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473540</v>
+        <v>473702</v>
       </c>
       <c r="R7" t="n">
-        <v>7046097</v>
+        <v>7046035</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1506,22 +1497,27 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1539,10 +1535,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121238387</v>
+        <v>121242466</v>
       </c>
       <c r="B8" t="n">
-        <v>79708</v>
+        <v>90705</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1551,45 +1547,53 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473540</v>
+        <v>473518</v>
       </c>
       <c r="R8" t="n">
-        <v>7046097</v>
+        <v>7045959</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1624,6 +1628,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1641,27 +1650,32 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>En smal död gran som är knäckt vid basen.</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1679,10 +1693,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121240324</v>
+        <v>121238339</v>
       </c>
       <c r="B9" t="n">
-        <v>79715</v>
+        <v>91370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1695,41 +1709,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473527</v>
+        <v>473540</v>
       </c>
       <c r="R9" t="n">
-        <v>7046057</v>
+        <v>7046097</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1786,27 +1796,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1824,10 +1829,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246722</v>
+        <v>121238387</v>
       </c>
       <c r="B10" t="n">
-        <v>79714</v>
+        <v>79708</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1840,41 +1845,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473702</v>
+        <v>473540</v>
       </c>
       <c r="R10" t="n">
-        <v>7046035</v>
+        <v>7046097</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1939,11 +1944,6 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>En flerstammig sälg.</t>
-        </is>
-      </c>
       <c r="AM10" t="inlineStr">
         <is>
           <t>Bark på levande träd</t>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2110,10 +2110,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121241235</v>
+        <v>121244830</v>
       </c>
       <c r="B12" t="n">
-        <v>79679</v>
+        <v>78598</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2126,30 +2126,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2157,10 +2153,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473521</v>
+        <v>473247</v>
       </c>
       <c r="R12" t="n">
-        <v>7046016</v>
+        <v>7045894</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2197,7 +2193,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2217,32 +2213,32 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>En grov sälglåga.</t>
+          <t>Flera granar.</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2260,7 +2256,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121244830</v>
+        <v>121231827</v>
       </c>
       <c r="B13" t="n">
         <v>78598</v>
@@ -2303,10 +2299,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473247</v>
+        <v>473583</v>
       </c>
       <c r="R13" t="n">
-        <v>7045894</v>
+        <v>7046084</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2343,7 +2339,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2363,7 +2359,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2376,11 +2372,6 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
       <c r="AM13" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -2388,7 +2379,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2406,10 +2397,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121231827</v>
+        <v>121241235</v>
       </c>
       <c r="B14" t="n">
-        <v>78598</v>
+        <v>79679</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2422,26 +2413,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2449,10 +2444,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473583</v>
+        <v>473521</v>
       </c>
       <c r="R14" t="n">
-        <v>7046084</v>
+        <v>7046016</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2489,7 +2484,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2514,22 +2509,27 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -3287,10 +3287,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121244747</v>
+        <v>121246191</v>
       </c>
       <c r="B20" t="n">
-        <v>56552</v>
+        <v>78334</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3303,53 +3303,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473482</v>
+        <v>473595</v>
       </c>
       <c r="R20" t="n">
-        <v>7045969</v>
+        <v>7046005</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3383,7 +3370,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3392,6 +3379,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3402,7 +3390,27 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3420,10 +3428,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121246191</v>
+        <v>121244747</v>
       </c>
       <c r="B21" t="n">
-        <v>78334</v>
+        <v>56552</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3436,40 +3444,53 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473595</v>
+        <v>473482</v>
       </c>
       <c r="R21" t="n">
-        <v>7046005</v>
+        <v>7045969</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3503,7 +3524,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3512,7 +3533,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3523,27 +3543,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Branddödat träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
+          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121246432</v>
+        <v>121241286</v>
       </c>
       <c r="B32" t="n">
-        <v>79680</v>
+        <v>79715</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5011,32 +5011,32 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473702</v>
+        <v>473521</v>
       </c>
       <c r="R32" t="n">
-        <v>7046035</v>
+        <v>7046016</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -5084,11 +5084,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -5121,17 +5116,17 @@
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>En flerstammig sälg.</t>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5149,10 +5144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121241286</v>
+        <v>121246432</v>
       </c>
       <c r="B33" t="n">
-        <v>79715</v>
+        <v>79680</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5161,32 +5156,32 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -5196,10 +5191,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473521</v>
+        <v>473702</v>
       </c>
       <c r="R33" t="n">
-        <v>7046016</v>
+        <v>7046035</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5234,6 +5229,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -5266,17 +5266,17 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>En grov sälglåga.</t>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 39937-2024 artfynd.xlsx
+++ b/artfynd/A 39937-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121219221</v>
+        <v>121219351</v>
       </c>
       <c r="B2" t="n">
-        <v>57348</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -723,14 +731,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473234</v>
+        <v>473214</v>
       </c>
       <c r="R2" t="n">
-        <v>7045879</v>
+        <v>7045971</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -767,7 +775,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +784,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,26 +796,6 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -827,7 +816,7 @@
         <v>121219127</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -962,10 +951,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121219351</v>
+        <v>121219221</v>
       </c>
       <c r="B4" t="n">
-        <v>98071</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -974,43 +963,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1018,14 +999,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473214</v>
+        <v>473234</v>
       </c>
       <c r="R4" t="n">
-        <v>7045971</v>
+        <v>7045879</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1062,7 +1043,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om färska ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1071,7 +1052,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1083,6 +1063,26 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1103,7 +1103,7 @@
         <v>121219485</v>
       </c>
       <c r="B5" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121240324</v>
+        <v>121242466</v>
       </c>
       <c r="B6" t="n">
-        <v>79715</v>
+        <v>90715</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1257,32 +1257,40 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1292,10 +1300,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473527</v>
+        <v>473518</v>
       </c>
       <c r="R6" t="n">
-        <v>7046057</v>
+        <v>7045959</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1330,6 +1338,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1347,32 +1360,32 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>En smal död gran som är knäckt vid basen.</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1390,10 +1403,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121246722</v>
+        <v>121246631</v>
       </c>
       <c r="B7" t="n">
-        <v>79714</v>
+        <v>79711</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1406,28 +1419,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1535,10 +1548,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121242466</v>
+        <v>121246191</v>
       </c>
       <c r="B8" t="n">
-        <v>90705</v>
+        <v>78337</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1551,38 +1564,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1590,13 +1591,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473518</v>
+        <v>473595</v>
       </c>
       <c r="R8" t="n">
-        <v>7045959</v>
+        <v>7046005</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1630,7 +1631,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1650,32 +1651,27 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>En smal död gran som är knäckt vid basen.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1693,10 +1689,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121238339</v>
+        <v>121241506</v>
       </c>
       <c r="B9" t="n">
-        <v>91370</v>
+        <v>78337</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1705,25 +1701,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1732,14 +1728,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473540</v>
+        <v>473522</v>
       </c>
       <c r="R9" t="n">
-        <v>7046097</v>
+        <v>7045984</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1774,6 +1770,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gott om kolflarnlav på en kolad tallhögstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1791,27 +1792,32 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>En ca 4 meter hög högstubbe.</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris # En ca 4 meter hög högstubbe.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1829,10 +1835,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121238387</v>
+        <v>121231824</v>
       </c>
       <c r="B10" t="n">
-        <v>79708</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1841,45 +1847,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473540</v>
+        <v>473642</v>
       </c>
       <c r="R10" t="n">
-        <v>7046097</v>
+        <v>7046059</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1914,6 +1916,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1936,22 +1943,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1969,10 +1976,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121231830</v>
+        <v>121231827</v>
       </c>
       <c r="B11" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2012,10 +2019,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473557</v>
+        <v>473583</v>
       </c>
       <c r="R11" t="n">
-        <v>7046096</v>
+        <v>7046084</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2052,7 +2059,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2110,10 +2117,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121244830</v>
+        <v>121244747</v>
       </c>
       <c r="B12" t="n">
-        <v>78598</v>
+        <v>56555</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2126,40 +2133,53 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473247</v>
+        <v>473482</v>
       </c>
       <c r="R12" t="n">
-        <v>7045894</v>
+        <v>7045969</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2193,7 +2213,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2202,7 +2222,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2213,32 +2232,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2256,10 +2250,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121231827</v>
+        <v>121246432</v>
       </c>
       <c r="B13" t="n">
-        <v>78598</v>
+        <v>79683</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2272,26 +2266,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2299,10 +2297,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473583</v>
+        <v>473702</v>
       </c>
       <c r="R13" t="n">
-        <v>7046084</v>
+        <v>7046035</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2339,7 +2337,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2364,22 +2362,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2397,10 +2400,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121241235</v>
+        <v>121238387</v>
       </c>
       <c r="B14" t="n">
-        <v>79679</v>
+        <v>79711</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2409,45 +2412,45 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473521</v>
+        <v>473540</v>
       </c>
       <c r="R14" t="n">
-        <v>7046016</v>
+        <v>7046097</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2482,11 +2485,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2517,19 +2515,14 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
-        </is>
-      </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2547,10 +2540,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121247565</v>
+        <v>121238149</v>
       </c>
       <c r="B15" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2563,41 +2556,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473680</v>
+        <v>473540</v>
       </c>
       <c r="R15" t="n">
-        <v>7046060</v>
+        <v>7046097</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2634,7 +2623,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2659,27 +2648,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2697,10 +2681,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121245981</v>
+        <v>121241235</v>
       </c>
       <c r="B16" t="n">
-        <v>90705</v>
+        <v>79682</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2713,28 +2697,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2744,13 +2728,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473515</v>
+        <v>473521</v>
       </c>
       <c r="R16" t="n">
-        <v>7045852</v>
+        <v>7046016</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2784,7 +2768,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2804,27 +2788,32 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, båhål (hackspettar) i grov asp, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2842,10 +2831,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121247541</v>
+        <v>121238082</v>
       </c>
       <c r="B17" t="n">
-        <v>79715</v>
+        <v>57351</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2854,45 +2843,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473680</v>
+        <v>473540</v>
       </c>
       <c r="R17" t="n">
-        <v>7046060</v>
+        <v>7046097</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2927,13 +2921,17 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2949,27 +2947,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2990,7 +2983,7 @@
         <v>121247570</v>
       </c>
       <c r="B18" t="n">
-        <v>79680</v>
+        <v>79683</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3137,10 +3130,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121238543</v>
+        <v>121246207</v>
       </c>
       <c r="B19" t="n">
-        <v>79679</v>
+        <v>90715</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3153,30 +3146,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3184,13 +3181,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473527</v>
+        <v>473595</v>
       </c>
       <c r="R19" t="n">
-        <v>7046057</v>
+        <v>7046005</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3224,7 +3221,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Fina exemplar av lunglav på en gammal sälg där vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Minst 8 st fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3244,32 +3241,27 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Horizontal, dead without ground contact # En upplyft lutande stam av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3287,10 +3279,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121246191</v>
+        <v>121240324</v>
       </c>
       <c r="B20" t="n">
-        <v>78334</v>
+        <v>79718</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3299,30 +3291,34 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3330,13 +3326,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473595</v>
+        <v>473527</v>
       </c>
       <c r="R20" t="n">
-        <v>7046005</v>
+        <v>7046057</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3366,11 +3362,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3390,27 +3381,32 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3428,10 +3424,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121244747</v>
+        <v>121247541</v>
       </c>
       <c r="B21" t="n">
-        <v>56552</v>
+        <v>79718</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3440,57 +3436,48 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473482</v>
+        <v>473680</v>
       </c>
       <c r="R21" t="n">
-        <v>7045969</v>
+        <v>7046060</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3522,17 +3509,13 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3543,7 +3526,32 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3561,10 +3569,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121245697</v>
+        <v>121246773</v>
       </c>
       <c r="B22" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3577,21 +3585,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3604,10 +3612,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473293</v>
+        <v>473688</v>
       </c>
       <c r="R22" t="n">
-        <v>7045728</v>
+        <v>7046072</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3644,7 +3652,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Enstaka stora bålar av lunglav några meter upp på en grovbarkad sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3664,27 +3672,27 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3702,10 +3710,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121241817</v>
+        <v>121246722</v>
       </c>
       <c r="B23" t="n">
-        <v>78598</v>
+        <v>79717</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3714,20 +3722,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3737,7 +3745,11 @@
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3745,10 +3757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473522</v>
+        <v>473702</v>
       </c>
       <c r="R23" t="n">
-        <v>7045984</v>
+        <v>7046035</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3783,11 +3795,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3805,27 +3812,32 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3843,10 +3855,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121246207</v>
+        <v>121245981</v>
       </c>
       <c r="B24" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3876,17 +3888,13 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3894,10 +3902,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473595</v>
+        <v>473515</v>
       </c>
       <c r="R24" t="n">
-        <v>7046005</v>
+        <v>7045852</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3934,7 +3942,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Minst 8 st fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3954,7 +3962,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, båhål (hackspettar) i grov asp, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -3974,7 +3982,7 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # En upplyft lutande stam av en knäckt gran. # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3992,10 +4000,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121231824</v>
+        <v>121241304</v>
       </c>
       <c r="B25" t="n">
-        <v>78598</v>
+        <v>79711</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -4004,30 +4012,34 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -4035,10 +4047,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473642</v>
+        <v>473521</v>
       </c>
       <c r="R25" t="n">
-        <v>7046059</v>
+        <v>7046016</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -4073,11 +4085,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -4100,22 +4107,27 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4133,10 +4145,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121241304</v>
+        <v>121244154</v>
       </c>
       <c r="B26" t="n">
-        <v>79708</v>
+        <v>78601</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4145,34 +4157,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -4180,10 +4188,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473521</v>
+        <v>473456</v>
       </c>
       <c r="R26" t="n">
-        <v>7046016</v>
+        <v>7045981</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4218,6 +4226,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -4235,32 +4248,27 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4278,10 +4286,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121238149</v>
+        <v>121231830</v>
       </c>
       <c r="B27" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4317,14 +4325,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473540</v>
+        <v>473557</v>
       </c>
       <c r="R27" t="n">
-        <v>7046097</v>
+        <v>7046096</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4361,7 +4369,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4419,10 +4427,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121238082</v>
+        <v>121241286</v>
       </c>
       <c r="B28" t="n">
-        <v>57348</v>
+        <v>79718</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4431,50 +4439,45 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473540</v>
+        <v>473521</v>
       </c>
       <c r="R28" t="n">
-        <v>7046097</v>
+        <v>7046016</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4509,17 +4512,13 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4535,22 +4534,27 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4568,10 +4572,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121245877</v>
+        <v>121244830</v>
       </c>
       <c r="B29" t="n">
-        <v>57364</v>
+        <v>78601</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4584,46 +4588,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473507</v>
+        <v>473247</v>
       </c>
       <c r="R29" t="n">
-        <v>7045849</v>
+        <v>7045894</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4660,7 +4655,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4669,6 +4664,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4679,7 +4675,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4692,14 +4688,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4717,10 +4718,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121246773</v>
+        <v>121241817</v>
       </c>
       <c r="B30" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4733,21 +4734,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4760,10 +4761,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473688</v>
+        <v>473522</v>
       </c>
       <c r="R30" t="n">
-        <v>7046072</v>
+        <v>7045984</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4800,7 +4801,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Enstaka stora bålar av lunglav några meter upp på en grovbarkad sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4820,27 +4821,27 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4858,10 +4859,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121244154</v>
+        <v>121238543</v>
       </c>
       <c r="B31" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4874,26 +4875,30 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4901,10 +4906,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473456</v>
+        <v>473527</v>
       </c>
       <c r="R31" t="n">
-        <v>7045981</v>
+        <v>7046057</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4941,7 +4946,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Fina exemplar av lunglav på en gammal sälg där vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4961,27 +4966,32 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4999,10 +5009,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121241286</v>
+        <v>121247565</v>
       </c>
       <c r="B32" t="n">
-        <v>79715</v>
+        <v>79682</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5011,32 +5021,32 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -5046,10 +5056,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473521</v>
+        <v>473680</v>
       </c>
       <c r="R32" t="n">
-        <v>7046016</v>
+        <v>7046060</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -5082,6 +5092,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Enstaka bålar av lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5144,10 +5159,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121246432</v>
+        <v>121245877</v>
       </c>
       <c r="B33" t="n">
-        <v>79680</v>
+        <v>57367</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5160,41 +5175,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473702</v>
+        <v>473507</v>
       </c>
       <c r="R33" t="n">
-        <v>7046035</v>
+        <v>7045849</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5231,7 +5251,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5240,7 +5260,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -5251,32 +5270,27 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>En flerstammig sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5294,10 +5308,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121246631</v>
+        <v>121245697</v>
       </c>
       <c r="B34" t="n">
-        <v>79708</v>
+        <v>78601</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5306,34 +5320,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -5341,10 +5351,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473702</v>
+        <v>473293</v>
       </c>
       <c r="R34" t="n">
-        <v>7046035</v>
+        <v>7045728</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5379,6 +5389,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -5396,32 +5411,27 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>En flerstammig sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5439,10 +5449,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121241506</v>
+        <v>121238339</v>
       </c>
       <c r="B35" t="n">
-        <v>78334</v>
+        <v>91380</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5451,25 +5461,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>3298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5478,14 +5488,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473522</v>
+        <v>473540</v>
       </c>
       <c r="R35" t="n">
-        <v>7045984</v>
+        <v>7046097</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5520,11 +5530,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Gott om kolflarnlav på en kolad tallhögstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5542,32 +5547,27 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>En ca 4 meter hög högstubbe.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris # En ca 4 meter hög högstubbe.</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5588,7 +5588,7 @@
         <v>121218973</v>
       </c>
       <c r="B36" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>121260476</v>
       </c>
       <c r="B37" t="n">
-        <v>74697</v>
+        <v>74700</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>

--- a/artfynd/A 39937-2024 artfynd.xlsx
+++ b/artfynd/A 39937-2024 artfynd.xlsx
@@ -2540,10 +2540,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121238149</v>
+        <v>121238082</v>
       </c>
       <c r="B15" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2556,27 +2556,36 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
@@ -2623,7 +2632,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2632,7 +2641,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2658,12 +2666,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2831,10 +2839,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121238082</v>
+        <v>121238149</v>
       </c>
       <c r="B17" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2847,36 +2855,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
@@ -2923,7 +2922,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2932,6 +2931,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2957,12 +2957,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -5308,10 +5308,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121245697</v>
+        <v>121238339</v>
       </c>
       <c r="B34" t="n">
-        <v>78601</v>
+        <v>91380</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5320,25 +5320,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -5347,14 +5347,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473293</v>
+        <v>473540</v>
       </c>
       <c r="R34" t="n">
-        <v>7045728</v>
+        <v>7046097</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5389,11 +5389,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -5411,7 +5406,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -5426,12 +5421,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5449,10 +5444,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121238339</v>
+        <v>121245697</v>
       </c>
       <c r="B35" t="n">
-        <v>91380</v>
+        <v>78601</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5461,25 +5456,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5488,14 +5483,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473540</v>
+        <v>473293</v>
       </c>
       <c r="R35" t="n">
-        <v>7046097</v>
+        <v>7045728</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5530,6 +5525,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>

--- a/artfynd/A 39937-2024 artfynd.xlsx
+++ b/artfynd/A 39937-2024 artfynd.xlsx
@@ -5308,10 +5308,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121238339</v>
+        <v>121245697</v>
       </c>
       <c r="B34" t="n">
-        <v>91380</v>
+        <v>78601</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5320,25 +5320,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -5347,14 +5347,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473540</v>
+        <v>473293</v>
       </c>
       <c r="R34" t="n">
-        <v>7046097</v>
+        <v>7045728</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5389,6 +5389,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -5406,7 +5411,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -5421,12 +5426,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5444,10 +5449,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121245697</v>
+        <v>121238339</v>
       </c>
       <c r="B35" t="n">
-        <v>78601</v>
+        <v>91380</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5456,25 +5461,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5483,14 +5488,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473293</v>
+        <v>473540</v>
       </c>
       <c r="R35" t="n">
-        <v>7045728</v>
+        <v>7046097</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5525,11 +5530,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>

--- a/artfynd/A 39937-2024 artfynd.xlsx
+++ b/artfynd/A 39937-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121219351</v>
+        <v>121219127</v>
       </c>
       <c r="B2" t="n">
         <v>98081</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473214</v>
+        <v>473560</v>
       </c>
       <c r="R2" t="n">
-        <v>7045971</v>
+        <v>7046115</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -775,7 +775,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Knärot med minst 33 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -813,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121219127</v>
+        <v>121219221</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>57351</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,43 +825,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -869,14 +861,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473560</v>
+        <v>473234</v>
       </c>
       <c r="R3" t="n">
-        <v>7046115</v>
+        <v>7045879</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -913,7 +905,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Knärot med minst 33 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om färska ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,7 +914,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -934,6 +925,26 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -951,7 +962,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121219221</v>
+        <v>121219485</v>
       </c>
       <c r="B4" t="n">
         <v>57351</v>
@@ -989,24 +1000,20 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473234</v>
+        <v>473631</v>
       </c>
       <c r="R4" t="n">
-        <v>7045879</v>
+        <v>7045992</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1043,7 +1050,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Äldre ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1100,10 +1107,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121219485</v>
+        <v>121219351</v>
       </c>
       <c r="B5" t="n">
-        <v>57351</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1112,46 +1119,58 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473631</v>
+        <v>473214</v>
       </c>
       <c r="R5" t="n">
-        <v>7045992</v>
+        <v>7045971</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1188,7 +1207,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1197,6 +1216,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1208,26 +1228,6 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121242466</v>
+        <v>121247570</v>
       </c>
       <c r="B6" t="n">
-        <v>90715</v>
+        <v>79683</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1261,36 +1261,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1300,10 +1292,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473518</v>
+        <v>473680</v>
       </c>
       <c r="R6" t="n">
-        <v>7045959</v>
+        <v>7046060</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1340,7 +1332,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Enstaka bålar av skrovellav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1360,32 +1352,32 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>En smal död gran som är knäckt vid basen.</t>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1403,7 +1395,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121246631</v>
+        <v>121241304</v>
       </c>
       <c r="B7" t="n">
         <v>79711</v>
@@ -1450,10 +1442,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473702</v>
+        <v>473521</v>
       </c>
       <c r="R7" t="n">
-        <v>7046035</v>
+        <v>7046016</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1520,17 +1512,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>En flerstammig sälg.</t>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1548,10 +1540,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121246191</v>
+        <v>121245697</v>
       </c>
       <c r="B8" t="n">
-        <v>78337</v>
+        <v>78601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1564,21 +1556,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1591,13 +1583,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473595</v>
+        <v>473293</v>
       </c>
       <c r="R8" t="n">
-        <v>7046005</v>
+        <v>7045728</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1631,7 +1623,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1651,27 +1643,27 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1689,10 +1681,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121241506</v>
+        <v>121244747</v>
       </c>
       <c r="B9" t="n">
-        <v>78337</v>
+        <v>56555</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1705,40 +1697,53 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473522</v>
+        <v>473482</v>
       </c>
       <c r="R9" t="n">
-        <v>7045984</v>
+        <v>7045969</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1772,7 +1777,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gott om kolflarnlav på en kolad tallhögstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1781,7 +1786,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1792,32 +1796,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>En ca 4 meter hög högstubbe.</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Branddödat träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris # En ca 4 meter hög högstubbe.</t>
+          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1835,10 +1814,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121231824</v>
+        <v>121246432</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>79683</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1851,26 +1830,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1878,10 +1861,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473642</v>
+        <v>473702</v>
       </c>
       <c r="R10" t="n">
-        <v>7046059</v>
+        <v>7046035</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1918,7 +1901,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1943,22 +1926,27 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1976,10 +1964,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121231827</v>
+        <v>121246773</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1992,21 +1980,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -2019,10 +2007,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473583</v>
+        <v>473688</v>
       </c>
       <c r="R11" t="n">
-        <v>7046084</v>
+        <v>7046072</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2059,7 +2047,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Enstaka stora bålar av lunglav några meter upp på en grovbarkad sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2084,22 +2072,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2117,10 +2105,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121244747</v>
+        <v>121242466</v>
       </c>
       <c r="B12" t="n">
-        <v>56555</v>
+        <v>90715</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2133,53 +2121,52 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473482</v>
+        <v>473518</v>
       </c>
       <c r="R12" t="n">
-        <v>7045969</v>
+        <v>7045959</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2222,6 +2209,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2232,7 +2220,32 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>En smal död gran som är knäckt vid basen.</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2250,10 +2263,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121246432</v>
+        <v>121247541</v>
       </c>
       <c r="B13" t="n">
-        <v>79683</v>
+        <v>79718</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2262,32 +2275,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2297,10 +2310,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473702</v>
+        <v>473680</v>
       </c>
       <c r="R13" t="n">
-        <v>7046035</v>
+        <v>7046060</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2335,11 +2348,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2372,17 +2380,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>En flerstammig sälg.</t>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2400,10 +2408,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121238387</v>
+        <v>121244154</v>
       </c>
       <c r="B14" t="n">
-        <v>79711</v>
+        <v>78601</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2412,45 +2420,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473540</v>
+        <v>473456</v>
       </c>
       <c r="R14" t="n">
-        <v>7046097</v>
+        <v>7045981</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2485,6 +2489,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2502,27 +2511,27 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2540,10 +2549,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121238082</v>
+        <v>121241506</v>
       </c>
       <c r="B15" t="n">
-        <v>57351</v>
+        <v>78337</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2556,46 +2565,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473540</v>
+        <v>473522</v>
       </c>
       <c r="R15" t="n">
-        <v>7046097</v>
+        <v>7045984</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om kolflarnlav på en kolad tallhögstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2641,6 +2641,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2651,27 +2652,32 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>En ca 4 meter hög högstubbe.</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris # En ca 4 meter hög högstubbe.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2689,10 +2695,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121241235</v>
+        <v>121238082</v>
       </c>
       <c r="B16" t="n">
-        <v>79682</v>
+        <v>57351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2705,41 +2711,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473521</v>
+        <v>473540</v>
       </c>
       <c r="R16" t="n">
-        <v>7046016</v>
+        <v>7046097</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2776,7 +2787,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2785,7 +2796,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2801,27 +2811,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2839,10 +2844,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121238149</v>
+        <v>121238339</v>
       </c>
       <c r="B17" t="n">
-        <v>78601</v>
+        <v>91380</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2851,25 +2856,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2920,11 +2925,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2957,12 +2957,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2980,10 +2980,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121247570</v>
+        <v>121244830</v>
       </c>
       <c r="B18" t="n">
-        <v>79683</v>
+        <v>78601</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2996,30 +2996,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -3027,10 +3023,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473680</v>
+        <v>473247</v>
       </c>
       <c r="R18" t="n">
-        <v>7046060</v>
+        <v>7045894</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3067,7 +3063,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Enstaka bålar av skrovellav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3087,32 +3083,32 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>En grov sälglåga.</t>
+          <t>Flera granar.</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3130,10 +3126,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121246207</v>
+        <v>121247565</v>
       </c>
       <c r="B19" t="n">
-        <v>90715</v>
+        <v>79682</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3146,34 +3142,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3181,13 +3173,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473595</v>
+        <v>473680</v>
       </c>
       <c r="R19" t="n">
-        <v>7046005</v>
+        <v>7046060</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3221,7 +3213,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Minst 8 st fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Enstaka bålar av lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3241,27 +3233,32 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # En upplyft lutande stam av en knäckt gran. # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3279,10 +3276,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121240324</v>
+        <v>121238149</v>
       </c>
       <c r="B20" t="n">
-        <v>79718</v>
+        <v>78601</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3291,45 +3288,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473527</v>
+        <v>473540</v>
       </c>
       <c r="R20" t="n">
-        <v>7046057</v>
+        <v>7046097</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3364,6 +3357,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3386,27 +3384,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3424,10 +3417,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121247541</v>
+        <v>121246631</v>
       </c>
       <c r="B21" t="n">
-        <v>79718</v>
+        <v>79711</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3440,21 +3433,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3471,10 +3464,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473680</v>
+        <v>473702</v>
       </c>
       <c r="R21" t="n">
-        <v>7046060</v>
+        <v>7046035</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3541,17 +3534,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>En grov sälglåga.</t>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3569,10 +3562,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121246773</v>
+        <v>121245981</v>
       </c>
       <c r="B22" t="n">
-        <v>79682</v>
+        <v>90715</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3585,26 +3578,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3612,13 +3609,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473688</v>
+        <v>473515</v>
       </c>
       <c r="R22" t="n">
-        <v>7046072</v>
+        <v>7045852</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3652,7 +3649,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Enstaka stora bålar av lunglav några meter upp på en grovbarkad sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3672,27 +3669,27 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, båhål (hackspettar) i grov asp, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3710,10 +3707,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121246722</v>
+        <v>121231824</v>
       </c>
       <c r="B23" t="n">
-        <v>79717</v>
+        <v>78601</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3722,20 +3719,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3745,11 +3742,7 @@
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3757,10 +3750,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473702</v>
+        <v>473642</v>
       </c>
       <c r="R23" t="n">
-        <v>7046035</v>
+        <v>7046059</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3795,6 +3788,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3817,27 +3815,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>En flerstammig sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3855,7 +3848,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121245981</v>
+        <v>121246207</v>
       </c>
       <c r="B24" t="n">
         <v>90715</v>
@@ -3888,13 +3881,17 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3902,10 +3899,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473515</v>
+        <v>473595</v>
       </c>
       <c r="R24" t="n">
-        <v>7045852</v>
+        <v>7046005</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3942,7 +3939,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Minst 8 st fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3962,7 +3959,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, båhål (hackspettar) i grov asp, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -3982,7 +3979,7 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies</t>
+          <t>Horizontal, dead without ground contact # En upplyft lutande stam av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -4000,10 +3997,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121241304</v>
+        <v>121241286</v>
       </c>
       <c r="B25" t="n">
-        <v>79711</v>
+        <v>79718</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -4016,21 +4013,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -4145,7 +4142,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121244154</v>
+        <v>121241817</v>
       </c>
       <c r="B26" t="n">
         <v>78601</v>
@@ -4188,10 +4185,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473456</v>
+        <v>473522</v>
       </c>
       <c r="R26" t="n">
-        <v>7045981</v>
+        <v>7045984</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4248,7 +4245,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -4286,7 +4283,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121231830</v>
+        <v>121231827</v>
       </c>
       <c r="B27" t="n">
         <v>78601</v>
@@ -4329,10 +4326,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473557</v>
+        <v>473583</v>
       </c>
       <c r="R27" t="n">
-        <v>7046096</v>
+        <v>7046084</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4369,7 +4366,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4427,10 +4424,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121241286</v>
+        <v>121246191</v>
       </c>
       <c r="B28" t="n">
-        <v>79718</v>
+        <v>78337</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4439,34 +4436,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4474,13 +4467,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473521</v>
+        <v>473595</v>
       </c>
       <c r="R28" t="n">
-        <v>7046016</v>
+        <v>7046005</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4510,6 +4503,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4529,32 +4527,27 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4572,7 +4565,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121244830</v>
+        <v>121231830</v>
       </c>
       <c r="B29" t="n">
         <v>78601</v>
@@ -4615,10 +4608,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473247</v>
+        <v>473557</v>
       </c>
       <c r="R29" t="n">
-        <v>7045894</v>
+        <v>7046096</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4655,7 +4648,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4675,7 +4668,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4688,11 +4681,6 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
       <c r="AM29" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -4700,7 +4688,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4718,10 +4706,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121241817</v>
+        <v>121241235</v>
       </c>
       <c r="B30" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4734,26 +4722,30 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4761,10 +4753,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473522</v>
+        <v>473521</v>
       </c>
       <c r="R30" t="n">
-        <v>7045984</v>
+        <v>7046016</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4801,7 +4793,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4821,27 +4813,32 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -5009,10 +5006,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121247565</v>
+        <v>121238387</v>
       </c>
       <c r="B32" t="n">
-        <v>79682</v>
+        <v>79711</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5021,45 +5018,45 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473680</v>
+        <v>473540</v>
       </c>
       <c r="R32" t="n">
-        <v>7046060</v>
+        <v>7046097</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -5094,11 +5091,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Enstaka bålar av lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -5129,19 +5121,14 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
-        </is>
-      </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5159,10 +5146,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121245877</v>
+        <v>121240324</v>
       </c>
       <c r="B33" t="n">
-        <v>57367</v>
+        <v>79718</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5171,50 +5158,45 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473507</v>
+        <v>473527</v>
       </c>
       <c r="R33" t="n">
-        <v>7045849</v>
+        <v>7046057</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5249,17 +5231,13 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -5270,27 +5248,32 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5308,10 +5291,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121245697</v>
+        <v>121246722</v>
       </c>
       <c r="B34" t="n">
-        <v>78601</v>
+        <v>79717</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5320,20 +5303,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5343,7 +5326,11 @@
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -5351,10 +5338,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473293</v>
+        <v>473702</v>
       </c>
       <c r="R34" t="n">
-        <v>7045728</v>
+        <v>7046035</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5389,11 +5376,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -5411,27 +5393,32 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5449,10 +5436,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121238339</v>
+        <v>121245877</v>
       </c>
       <c r="B35" t="n">
-        <v>91380</v>
+        <v>57367</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5461,41 +5448,50 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473540</v>
+        <v>473507</v>
       </c>
       <c r="R35" t="n">
-        <v>7046097</v>
+        <v>7045849</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5530,13 +5526,17 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121218973</v>
+        <v>121260476</v>
       </c>
       <c r="B36" t="n">
-        <v>90697</v>
+        <v>74700</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5601,21 +5601,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5628,13 +5628,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473506</v>
+        <v>473489</v>
       </c>
       <c r="R36" t="n">
-        <v>7046084</v>
+        <v>7046095</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5693,22 +5693,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Wood surface of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5726,10 +5726,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121260476</v>
+        <v>121218973</v>
       </c>
       <c r="B37" t="n">
-        <v>74700</v>
+        <v>90697</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5742,21 +5742,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5769,13 +5769,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473489</v>
+        <v>473506</v>
       </c>
       <c r="R37" t="n">
-        <v>7046095</v>
+        <v>7046084</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5834,22 +5834,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Betula</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>

--- a/artfynd/A 39937-2024 artfynd.xlsx
+++ b/artfynd/A 39937-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121219127</v>
+        <v>121219221</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>57351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -731,14 +723,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473560</v>
+        <v>473234</v>
       </c>
       <c r="R2" t="n">
-        <v>7046115</v>
+        <v>7045879</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -775,7 +767,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Knärot med minst 33 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om färska ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +776,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,6 +787,26 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -813,10 +824,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121219221</v>
+        <v>121219351</v>
       </c>
       <c r="B3" t="n">
-        <v>57351</v>
+        <v>98094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,35 +836,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -861,14 +880,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473234</v>
+        <v>473214</v>
       </c>
       <c r="R3" t="n">
-        <v>7045879</v>
+        <v>7045971</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -905,7 +924,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,6 +933,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -925,26 +945,6 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121219351</v>
+        <v>121219127</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473214</v>
+        <v>473560</v>
       </c>
       <c r="R5" t="n">
-        <v>7045971</v>
+        <v>7046115</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Knärot med minst 33 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121247570</v>
+        <v>121241286</v>
       </c>
       <c r="B6" t="n">
-        <v>79683</v>
+        <v>79721</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473680</v>
+        <v>473521</v>
       </c>
       <c r="R6" t="n">
-        <v>7046060</v>
+        <v>7046016</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1328,11 +1328,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Enstaka bålar av skrovellav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1395,10 +1390,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121241304</v>
+        <v>121247565</v>
       </c>
       <c r="B7" t="n">
-        <v>79711</v>
+        <v>79685</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1407,32 +1402,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1442,10 +1437,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473521</v>
+        <v>473680</v>
       </c>
       <c r="R7" t="n">
-        <v>7046016</v>
+        <v>7046060</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1478,6 +1473,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Enstaka bålar av lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1540,10 +1540,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121245697</v>
+        <v>121241817</v>
       </c>
       <c r="B8" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473293</v>
+        <v>473522</v>
       </c>
       <c r="R8" t="n">
-        <v>7045728</v>
+        <v>7045984</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1681,10 +1681,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121244747</v>
+        <v>121245981</v>
       </c>
       <c r="B9" t="n">
-        <v>56555</v>
+        <v>90727</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1697,53 +1697,44 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473482</v>
+        <v>473515</v>
       </c>
       <c r="R9" t="n">
-        <v>7045969</v>
+        <v>7045852</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1786,6 +1777,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1796,7 +1788,27 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, båhål (hackspettar) i grov asp, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1814,10 +1826,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246432</v>
+        <v>121241304</v>
       </c>
       <c r="B10" t="n">
-        <v>79683</v>
+        <v>79714</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1826,32 +1838,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1861,10 +1873,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473702</v>
+        <v>473521</v>
       </c>
       <c r="R10" t="n">
-        <v>7046035</v>
+        <v>7046016</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1899,11 +1911,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1936,17 +1943,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>En flerstammig sälg.</t>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1964,10 +1971,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121246773</v>
+        <v>121231824</v>
       </c>
       <c r="B11" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1980,21 +1987,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -2007,10 +2014,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473688</v>
+        <v>473642</v>
       </c>
       <c r="R11" t="n">
-        <v>7046072</v>
+        <v>7046059</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2047,7 +2054,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Enstaka stora bålar av lunglav några meter upp på en grovbarkad sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2072,22 +2079,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2105,10 +2112,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121242466</v>
+        <v>121238149</v>
       </c>
       <c r="B12" t="n">
-        <v>90715</v>
+        <v>78604</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2121,49 +2128,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473518</v>
+        <v>473540</v>
       </c>
       <c r="R12" t="n">
-        <v>7045959</v>
+        <v>7046097</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2200,7 +2195,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2220,7 +2215,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2233,19 +2228,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>En smal död gran som är knäckt vid basen.</t>
-        </is>
-      </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2263,10 +2253,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121247541</v>
+        <v>121238387</v>
       </c>
       <c r="B13" t="n">
-        <v>79718</v>
+        <v>79714</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2279,21 +2269,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2306,14 +2296,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473680</v>
+        <v>473540</v>
       </c>
       <c r="R13" t="n">
-        <v>7046060</v>
+        <v>7046097</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2378,19 +2368,14 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
-        </is>
-      </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2408,10 +2393,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121244154</v>
+        <v>121231827</v>
       </c>
       <c r="B14" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2451,10 +2436,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473456</v>
+        <v>473583</v>
       </c>
       <c r="R14" t="n">
-        <v>7045981</v>
+        <v>7046084</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2491,7 +2476,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2511,7 +2496,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2549,10 +2534,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121241506</v>
+        <v>121238543</v>
       </c>
       <c r="B15" t="n">
-        <v>78337</v>
+        <v>79685</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2565,26 +2550,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2592,10 +2581,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473522</v>
+        <v>473527</v>
       </c>
       <c r="R15" t="n">
-        <v>7045984</v>
+        <v>7046057</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2632,7 +2621,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gott om kolflarnlav på en kolad tallhögstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Fina exemplar av lunglav på en gammal sälg där vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2652,32 +2641,32 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>En ca 4 meter hög högstubbe.</t>
+          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris # En ca 4 meter hög högstubbe.</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2695,10 +2684,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121238082</v>
+        <v>121245877</v>
       </c>
       <c r="B16" t="n">
-        <v>57351</v>
+        <v>57367</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2711,16 +2700,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2733,7 +2722,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2743,14 +2732,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473540</v>
+        <v>473507</v>
       </c>
       <c r="R16" t="n">
-        <v>7046097</v>
+        <v>7045849</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2787,7 +2776,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2806,7 +2795,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2826,7 +2815,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2844,10 +2833,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121238339</v>
+        <v>121244747</v>
       </c>
       <c r="B17" t="n">
-        <v>91380</v>
+        <v>56555</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2856,44 +2845,57 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473540</v>
+        <v>473482</v>
       </c>
       <c r="R17" t="n">
-        <v>7046097</v>
+        <v>7045969</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2925,13 +2927,17 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2942,27 +2948,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2980,10 +2966,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121244830</v>
+        <v>121247570</v>
       </c>
       <c r="B18" t="n">
-        <v>78601</v>
+        <v>79686</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2996,26 +2982,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -3023,10 +3013,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473247</v>
+        <v>473680</v>
       </c>
       <c r="R18" t="n">
-        <v>7045894</v>
+        <v>7046060</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3063,7 +3053,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Enstaka bålar av skrovellav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3083,32 +3073,32 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Flera granar.</t>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3126,10 +3116,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121247565</v>
+        <v>121246631</v>
       </c>
       <c r="B19" t="n">
-        <v>79682</v>
+        <v>79714</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3138,32 +3128,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -3173,10 +3163,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473680</v>
+        <v>473702</v>
       </c>
       <c r="R19" t="n">
-        <v>7046060</v>
+        <v>7046035</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3211,11 +3201,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Enstaka bålar av lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3248,17 +3233,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>En grov sälglåga.</t>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3276,10 +3261,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121238149</v>
+        <v>121231830</v>
       </c>
       <c r="B20" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3315,14 +3300,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473540</v>
+        <v>473557</v>
       </c>
       <c r="R20" t="n">
-        <v>7046097</v>
+        <v>7046096</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3359,7 +3344,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3417,10 +3402,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121246631</v>
+        <v>121246191</v>
       </c>
       <c r="B21" t="n">
-        <v>79711</v>
+        <v>78340</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3429,34 +3414,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3464,13 +3445,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473702</v>
+        <v>473595</v>
       </c>
       <c r="R21" t="n">
-        <v>7046035</v>
+        <v>7046005</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3500,6 +3481,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3519,32 +3505,27 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>En flerstammig sälg.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3562,10 +3543,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121245981</v>
+        <v>121241235</v>
       </c>
       <c r="B22" t="n">
-        <v>90715</v>
+        <v>79685</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3578,28 +3559,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3609,13 +3590,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473515</v>
+        <v>473521</v>
       </c>
       <c r="R22" t="n">
-        <v>7045852</v>
+        <v>7046016</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3649,7 +3630,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3669,27 +3650,32 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, båhål (hackspettar) i grov asp, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3707,10 +3693,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121231824</v>
+        <v>121246432</v>
       </c>
       <c r="B23" t="n">
-        <v>78601</v>
+        <v>79686</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3723,26 +3709,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3750,10 +3740,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473642</v>
+        <v>473702</v>
       </c>
       <c r="R23" t="n">
-        <v>7046059</v>
+        <v>7046035</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3790,7 +3780,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3815,22 +3805,27 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3848,10 +3843,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121246207</v>
+        <v>121241506</v>
       </c>
       <c r="B24" t="n">
-        <v>90715</v>
+        <v>78340</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3864,33 +3859,25 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3899,13 +3886,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473595</v>
+        <v>473522</v>
       </c>
       <c r="R24" t="n">
-        <v>7046005</v>
+        <v>7045984</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3939,7 +3926,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Minst 8 st fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om kolflarnlav på en kolad tallhögstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3964,22 +3951,27 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>En ca 4 meter hög högstubbe.</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # En upplyft lutande stam av en knäckt gran. # Picea abies</t>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris # En ca 4 meter hög högstubbe.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3997,10 +3989,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121241286</v>
+        <v>121240324</v>
       </c>
       <c r="B25" t="n">
-        <v>79718</v>
+        <v>79721</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -4044,10 +4036,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473521</v>
+        <v>473527</v>
       </c>
       <c r="R25" t="n">
-        <v>7046016</v>
+        <v>7046057</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -4114,17 +4106,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>En grov sälglåga.</t>
+          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4142,10 +4134,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121241817</v>
+        <v>121242466</v>
       </c>
       <c r="B26" t="n">
-        <v>78601</v>
+        <v>90727</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4158,26 +4150,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -4185,10 +4189,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473522</v>
+        <v>473518</v>
       </c>
       <c r="R26" t="n">
-        <v>7045984</v>
+        <v>7045959</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4225,7 +4229,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4245,7 +4249,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -4258,14 +4262,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>En smal död gran som är knäckt vid basen.</t>
+        </is>
+      </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4283,10 +4292,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121231827</v>
+        <v>121245697</v>
       </c>
       <c r="B27" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4326,10 +4335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473583</v>
+        <v>473293</v>
       </c>
       <c r="R27" t="n">
-        <v>7046084</v>
+        <v>7045728</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4366,7 +4375,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4386,7 +4395,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -4424,10 +4433,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121246191</v>
+        <v>121247541</v>
       </c>
       <c r="B28" t="n">
-        <v>78337</v>
+        <v>79721</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4436,30 +4445,34 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4467,13 +4480,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473595</v>
+        <v>473680</v>
       </c>
       <c r="R28" t="n">
-        <v>7046005</v>
+        <v>7046060</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4503,11 +4516,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4527,27 +4535,32 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4565,10 +4578,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121231830</v>
+        <v>121238339</v>
       </c>
       <c r="B29" t="n">
-        <v>78601</v>
+        <v>91392</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4577,25 +4590,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4604,14 +4617,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473557</v>
+        <v>473540</v>
       </c>
       <c r="R29" t="n">
-        <v>7046096</v>
+        <v>7046097</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4646,11 +4659,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4683,12 +4691,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4706,10 +4714,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121241235</v>
+        <v>121246207</v>
       </c>
       <c r="B30" t="n">
-        <v>79682</v>
+        <v>90727</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4722,30 +4730,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4753,13 +4765,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473521</v>
+        <v>473595</v>
       </c>
       <c r="R30" t="n">
-        <v>7046016</v>
+        <v>7046005</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4793,7 +4805,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Minst 8 st fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4813,32 +4825,27 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Horizontal, dead without ground contact # En upplyft lutande stam av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4856,10 +4863,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121238543</v>
+        <v>121238082</v>
       </c>
       <c r="B31" t="n">
-        <v>79682</v>
+        <v>57351</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4872,41 +4879,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473527</v>
+        <v>473540</v>
       </c>
       <c r="R31" t="n">
-        <v>7046057</v>
+        <v>7046097</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4943,7 +4955,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Fina exemplar av lunglav på en gammal sälg där vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4952,7 +4964,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4968,27 +4979,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -5006,10 +5012,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121238387</v>
+        <v>121246722</v>
       </c>
       <c r="B32" t="n">
-        <v>79711</v>
+        <v>79720</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5022,41 +5028,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473540</v>
+        <v>473702</v>
       </c>
       <c r="R32" t="n">
-        <v>7046097</v>
+        <v>7046035</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -5121,6 +5127,11 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>En flerstammig sälg.</t>
+        </is>
+      </c>
       <c r="AM32" t="inlineStr">
         <is>
           <t>Bark på levande träd</t>
@@ -5128,7 +5139,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5146,10 +5157,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121240324</v>
+        <v>121246773</v>
       </c>
       <c r="B33" t="n">
-        <v>79718</v>
+        <v>79685</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5158,34 +5169,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -5193,10 +5200,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473527</v>
+        <v>473688</v>
       </c>
       <c r="R33" t="n">
-        <v>7046057</v>
+        <v>7046072</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5231,6 +5238,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Enstaka stora bålar av lunglav några meter upp på en grovbarkad sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -5261,11 +5273,6 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
-        </is>
-      </c>
       <c r="AM33" t="inlineStr">
         <is>
           <t>Bark på levande träd</t>
@@ -5273,7 +5280,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5291,10 +5298,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121246722</v>
+        <v>121244830</v>
       </c>
       <c r="B34" t="n">
-        <v>79717</v>
+        <v>78604</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5303,20 +5310,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5326,11 +5333,7 @@
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -5338,10 +5341,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473702</v>
+        <v>473247</v>
       </c>
       <c r="R34" t="n">
-        <v>7046035</v>
+        <v>7045894</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5376,6 +5379,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -5393,32 +5401,32 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>En flerstammig sälg.</t>
+          <t>Flera granar.</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5436,10 +5444,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121245877</v>
+        <v>121244154</v>
       </c>
       <c r="B35" t="n">
-        <v>57367</v>
+        <v>78604</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5452,46 +5460,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473507</v>
+        <v>473456</v>
       </c>
       <c r="R35" t="n">
-        <v>7045849</v>
+        <v>7045981</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5528,7 +5527,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5537,6 +5536,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121260476</v>
+        <v>121218973</v>
       </c>
       <c r="B36" t="n">
-        <v>74700</v>
+        <v>90709</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5601,21 +5601,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5628,13 +5628,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473489</v>
+        <v>473506</v>
       </c>
       <c r="R36" t="n">
-        <v>7046095</v>
+        <v>7046084</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5693,22 +5693,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Betula</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5726,10 +5726,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121218973</v>
+        <v>121260476</v>
       </c>
       <c r="B37" t="n">
-        <v>90697</v>
+        <v>74702</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5742,21 +5742,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5769,13 +5769,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473506</v>
+        <v>473489</v>
       </c>
       <c r="R37" t="n">
-        <v>7046084</v>
+        <v>7046095</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5834,22 +5834,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Wood surface of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>

--- a/artfynd/A 39937-2024 artfynd.xlsx
+++ b/artfynd/A 39937-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121219221</v>
+        <v>121219127</v>
       </c>
       <c r="B2" t="n">
-        <v>57351</v>
+        <v>98095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -723,14 +731,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473234</v>
+        <v>473560</v>
       </c>
       <c r="R2" t="n">
-        <v>7045879</v>
+        <v>7046115</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -767,7 +775,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Knärot med minst 33 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +784,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,26 +796,6 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -824,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121219351</v>
+        <v>121219221</v>
       </c>
       <c r="B3" t="n">
-        <v>98094</v>
+        <v>57351</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,43 +825,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -880,14 +861,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473214</v>
+        <v>473234</v>
       </c>
       <c r="R3" t="n">
-        <v>7045971</v>
+        <v>7045879</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -924,7 +905,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om färska ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,7 +914,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -945,6 +925,26 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121219127</v>
+        <v>121219351</v>
       </c>
       <c r="B5" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473560</v>
+        <v>473214</v>
       </c>
       <c r="R5" t="n">
-        <v>7046115</v>
+        <v>7045971</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Knärot med minst 33 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121241286</v>
+        <v>121238387</v>
       </c>
       <c r="B6" t="n">
-        <v>79721</v>
+        <v>79714</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1261,21 +1261,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1288,14 +1288,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473521</v>
+        <v>473540</v>
       </c>
       <c r="R6" t="n">
-        <v>7046016</v>
+        <v>7046097</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1360,19 +1360,14 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
-        </is>
-      </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1390,7 +1385,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121247565</v>
+        <v>121238543</v>
       </c>
       <c r="B7" t="n">
         <v>79685</v>
@@ -1427,7 +1422,7 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1437,10 +1432,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473680</v>
+        <v>473527</v>
       </c>
       <c r="R7" t="n">
-        <v>7046060</v>
+        <v>7046057</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1477,7 +1472,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Fina exemplar av lunglav på en gammal sälg där vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1512,17 +1507,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>En grov sälglåga.</t>
+          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1540,10 +1535,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121241817</v>
+        <v>121238082</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
+        <v>57351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1556,37 +1551,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473522</v>
+        <v>473540</v>
       </c>
       <c r="R8" t="n">
-        <v>7045984</v>
+        <v>7046097</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1623,7 +1627,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1632,7 +1636,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1643,7 +1646,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1658,12 +1661,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1681,10 +1684,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121245981</v>
+        <v>121241817</v>
       </c>
       <c r="B9" t="n">
-        <v>90727</v>
+        <v>78604</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1697,30 +1700,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1728,13 +1727,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473515</v>
+        <v>473522</v>
       </c>
       <c r="R9" t="n">
-        <v>7045852</v>
+        <v>7045984</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1768,7 +1767,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1788,7 +1787,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, båhål (hackspettar) i grov asp, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1803,12 +1802,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1826,10 +1825,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121241304</v>
+        <v>121241506</v>
       </c>
       <c r="B10" t="n">
-        <v>79714</v>
+        <v>78340</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1838,34 +1837,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1873,10 +1868,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473521</v>
+        <v>473522</v>
       </c>
       <c r="R10" t="n">
-        <v>7046016</v>
+        <v>7045984</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1911,6 +1906,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gott om kolflarnlav på en kolad tallhögstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1928,32 +1928,32 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>En grov sälglåga.</t>
+          <t>En ca 4 meter hög högstubbe.</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris # En ca 4 meter hög högstubbe.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121231824</v>
+        <v>121247565</v>
       </c>
       <c r="B11" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1987,26 +1987,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -2014,10 +2018,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473642</v>
+        <v>473680</v>
       </c>
       <c r="R11" t="n">
-        <v>7046059</v>
+        <v>7046060</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2054,7 +2058,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Enstaka bålar av lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2079,22 +2083,27 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2112,10 +2121,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121238149</v>
+        <v>121241235</v>
       </c>
       <c r="B12" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2128,37 +2137,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473540</v>
+        <v>473521</v>
       </c>
       <c r="R12" t="n">
-        <v>7046097</v>
+        <v>7046016</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2195,7 +2208,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2220,22 +2233,27 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2253,10 +2271,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121238387</v>
+        <v>121246773</v>
       </c>
       <c r="B13" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2265,45 +2283,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473540</v>
+        <v>473688</v>
       </c>
       <c r="R13" t="n">
-        <v>7046097</v>
+        <v>7046072</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2338,6 +2352,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Enstaka stora bålar av lunglav några meter upp på en grovbarkad sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2375,7 +2394,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2393,10 +2412,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121231827</v>
+        <v>121247541</v>
       </c>
       <c r="B14" t="n">
-        <v>78604</v>
+        <v>79721</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2405,30 +2424,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2436,10 +2459,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473583</v>
+        <v>473680</v>
       </c>
       <c r="R14" t="n">
-        <v>7046084</v>
+        <v>7046060</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2474,11 +2497,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2501,22 +2519,27 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2534,10 +2557,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121238543</v>
+        <v>121242466</v>
       </c>
       <c r="B15" t="n">
-        <v>79685</v>
+        <v>90728</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2550,28 +2573,36 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2581,10 +2612,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473527</v>
+        <v>473518</v>
       </c>
       <c r="R15" t="n">
-        <v>7046057</v>
+        <v>7045959</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2621,7 +2652,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Fina exemplar av lunglav på en gammal sälg där vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2641,32 +2672,32 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>En smal död gran som är knäckt vid basen.</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2684,10 +2715,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121245877</v>
+        <v>121247570</v>
       </c>
       <c r="B16" t="n">
-        <v>57367</v>
+        <v>79686</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2700,46 +2731,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473507</v>
+        <v>473680</v>
       </c>
       <c r="R16" t="n">
-        <v>7045849</v>
+        <v>7046060</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2776,7 +2802,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Enstaka bålar av skrovellav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2785,6 +2811,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2795,27 +2822,32 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2833,10 +2865,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121244747</v>
+        <v>121246631</v>
       </c>
       <c r="B17" t="n">
-        <v>56555</v>
+        <v>79714</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2845,57 +2877,48 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473482</v>
+        <v>473702</v>
       </c>
       <c r="R17" t="n">
-        <v>7045969</v>
+        <v>7046035</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2927,17 +2950,13 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2948,7 +2967,32 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>En flerstammig sälg.</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2966,10 +3010,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121247570</v>
+        <v>121246191</v>
       </c>
       <c r="B18" t="n">
-        <v>79686</v>
+        <v>78340</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2982,30 +3026,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -3013,13 +3053,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473680</v>
+        <v>473595</v>
       </c>
       <c r="R18" t="n">
-        <v>7046060</v>
+        <v>7046005</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3053,7 +3093,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Enstaka bålar av skrovellav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3073,32 +3113,27 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3116,10 +3151,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121246631</v>
+        <v>121244154</v>
       </c>
       <c r="B19" t="n">
-        <v>79714</v>
+        <v>78604</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3128,34 +3163,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3163,10 +3194,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473702</v>
+        <v>473456</v>
       </c>
       <c r="R19" t="n">
-        <v>7046035</v>
+        <v>7045981</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3201,6 +3232,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3218,32 +3254,27 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>En flerstammig sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3261,7 +3292,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121231830</v>
+        <v>121231827</v>
       </c>
       <c r="B20" t="n">
         <v>78604</v>
@@ -3304,10 +3335,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473557</v>
+        <v>473583</v>
       </c>
       <c r="R20" t="n">
-        <v>7046096</v>
+        <v>7046084</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3344,7 +3375,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3402,10 +3433,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121246191</v>
+        <v>121245981</v>
       </c>
       <c r="B21" t="n">
-        <v>78340</v>
+        <v>90728</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3418,26 +3449,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3445,10 +3480,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473595</v>
+        <v>473515</v>
       </c>
       <c r="R21" t="n">
-        <v>7046005</v>
+        <v>7045852</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3485,7 +3520,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3505,27 +3540,27 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, båhål (hackspettar) i grov asp, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
+          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3543,10 +3578,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121241235</v>
+        <v>121231830</v>
       </c>
       <c r="B22" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3559,30 +3594,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3590,10 +3621,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473521</v>
+        <v>473557</v>
       </c>
       <c r="R22" t="n">
-        <v>7046016</v>
+        <v>7046096</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3630,7 +3661,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3655,27 +3686,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3693,10 +3719,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121246432</v>
+        <v>121245697</v>
       </c>
       <c r="B23" t="n">
-        <v>79686</v>
+        <v>78604</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3709,30 +3735,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3740,10 +3762,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473702</v>
+        <v>473293</v>
       </c>
       <c r="R23" t="n">
-        <v>7046035</v>
+        <v>7045728</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3780,7 +3802,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3800,32 +3822,27 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>En flerstammig sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3843,10 +3860,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121241506</v>
+        <v>121246207</v>
       </c>
       <c r="B24" t="n">
-        <v>78340</v>
+        <v>90728</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3859,25 +3876,33 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3886,13 +3911,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473522</v>
+        <v>473595</v>
       </c>
       <c r="R24" t="n">
-        <v>7045984</v>
+        <v>7046005</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3926,7 +3951,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gott om kolflarnlav på en kolad tallhögstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Minst 8 st fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3951,27 +3976,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>En ca 4 meter hög högstubbe.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris # En ca 4 meter hög högstubbe.</t>
+          <t>Horizontal, dead without ground contact # En upplyft lutande stam av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3989,10 +4009,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121240324</v>
+        <v>121244830</v>
       </c>
       <c r="B25" t="n">
-        <v>79721</v>
+        <v>78604</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -4001,34 +4021,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -4036,10 +4052,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473527</v>
+        <v>473247</v>
       </c>
       <c r="R25" t="n">
-        <v>7046057</v>
+        <v>7045894</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -4074,6 +4090,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -4091,32 +4112,32 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Flera granar.</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4134,10 +4155,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121242466</v>
+        <v>121238339</v>
       </c>
       <c r="B26" t="n">
-        <v>90727</v>
+        <v>91393</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4146,53 +4167,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473518</v>
+        <v>473540</v>
       </c>
       <c r="R26" t="n">
-        <v>7045959</v>
+        <v>7046097</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4227,11 +4236,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -4249,7 +4253,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -4262,19 +4266,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>En smal död gran som är knäckt vid basen.</t>
-        </is>
-      </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4292,10 +4291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121245697</v>
+        <v>121241286</v>
       </c>
       <c r="B27" t="n">
-        <v>78604</v>
+        <v>79721</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4304,30 +4303,34 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4335,10 +4338,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473293</v>
+        <v>473521</v>
       </c>
       <c r="R27" t="n">
-        <v>7045728</v>
+        <v>7046016</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4373,11 +4376,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4395,27 +4393,32 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4433,10 +4436,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121247541</v>
+        <v>121246722</v>
       </c>
       <c r="B28" t="n">
-        <v>79721</v>
+        <v>79720</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4449,28 +4452,28 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4480,10 +4483,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473680</v>
+        <v>473702</v>
       </c>
       <c r="R28" t="n">
-        <v>7046060</v>
+        <v>7046035</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4550,17 +4553,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>En grov sälglåga.</t>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4578,10 +4581,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121238339</v>
+        <v>121245877</v>
       </c>
       <c r="B29" t="n">
-        <v>91392</v>
+        <v>57367</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4590,41 +4593,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473540</v>
+        <v>473507</v>
       </c>
       <c r="R29" t="n">
-        <v>7046097</v>
+        <v>7045849</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4659,13 +4671,17 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4676,7 +4692,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4691,12 +4707,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4714,10 +4730,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121246207</v>
+        <v>121238149</v>
       </c>
       <c r="B30" t="n">
-        <v>90727</v>
+        <v>78604</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4730,48 +4746,40 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473595</v>
+        <v>473540</v>
       </c>
       <c r="R30" t="n">
-        <v>7046005</v>
+        <v>7046097</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4805,7 +4813,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Minst 8 st fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4825,7 +4833,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4840,12 +4848,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # En upplyft lutande stam av en knäckt gran. # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4863,10 +4871,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121238082</v>
+        <v>121244747</v>
       </c>
       <c r="B31" t="n">
-        <v>57351</v>
+        <v>56555</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4879,16 +4887,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4896,12 +4904,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4915,13 +4927,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473540</v>
+        <v>473482</v>
       </c>
       <c r="R31" t="n">
-        <v>7046097</v>
+        <v>7045969</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4974,27 +4986,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -5012,10 +5004,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121246722</v>
+        <v>121246432</v>
       </c>
       <c r="B32" t="n">
-        <v>79720</v>
+        <v>79686</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5024,25 +5016,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -5095,6 +5087,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5157,10 +5154,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121246773</v>
+        <v>121241304</v>
       </c>
       <c r="B33" t="n">
-        <v>79685</v>
+        <v>79714</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5169,30 +5166,34 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -5200,10 +5201,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473688</v>
+        <v>473521</v>
       </c>
       <c r="R33" t="n">
-        <v>7046072</v>
+        <v>7046016</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5238,11 +5239,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Enstaka stora bålar av lunglav några meter upp på en grovbarkad sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -5273,14 +5269,19 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
+        </is>
+      </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5298,7 +5299,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121244830</v>
+        <v>121231824</v>
       </c>
       <c r="B34" t="n">
         <v>78604</v>
@@ -5341,10 +5342,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473247</v>
+        <v>473642</v>
       </c>
       <c r="R34" t="n">
-        <v>7045894</v>
+        <v>7046059</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5381,7 +5382,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5401,7 +5402,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -5414,11 +5415,6 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
       <c r="AM34" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -5426,7 +5422,7 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5444,10 +5440,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121244154</v>
+        <v>121240324</v>
       </c>
       <c r="B35" t="n">
-        <v>78604</v>
+        <v>79721</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5456,30 +5452,34 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473456</v>
+        <v>473527</v>
       </c>
       <c r="R35" t="n">
-        <v>7045981</v>
+        <v>7046057</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5525,11 +5525,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5547,27 +5542,32 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5588,7 +5588,7 @@
         <v>121218973</v>
       </c>
       <c r="B36" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 39937-2024 artfynd.xlsx
+++ b/artfynd/A 39937-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121219127</v>
+        <v>121219351</v>
       </c>
       <c r="B2" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473560</v>
+        <v>473214</v>
       </c>
       <c r="R2" t="n">
-        <v>7046115</v>
+        <v>7045971</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -775,7 +775,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Knärot med minst 33 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -813,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121219221</v>
+        <v>121219127</v>
       </c>
       <c r="B3" t="n">
-        <v>57351</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,35 +825,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -861,14 +869,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473234</v>
+        <v>473560</v>
       </c>
       <c r="R3" t="n">
-        <v>7045879</v>
+        <v>7046115</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -905,7 +913,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Knärot med minst 33 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,6 +922,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -925,26 +934,6 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -962,10 +951,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121219485</v>
+        <v>121219221</v>
       </c>
       <c r="B4" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1000,20 +989,24 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473631</v>
+        <v>473234</v>
       </c>
       <c r="R4" t="n">
-        <v>7045992</v>
+        <v>7045879</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1050,7 +1043,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om färska ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1107,10 +1100,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121219351</v>
+        <v>121219485</v>
       </c>
       <c r="B5" t="n">
-        <v>98095</v>
+        <v>57354</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1119,58 +1112,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473214</v>
+        <v>473631</v>
       </c>
       <c r="R5" t="n">
-        <v>7045971</v>
+        <v>7045992</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1207,7 +1188,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Äldre ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1216,7 +1197,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1228,6 +1208,26 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121238387</v>
+        <v>121244830</v>
       </c>
       <c r="B6" t="n">
-        <v>79714</v>
+        <v>78607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1257,45 +1257,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473540</v>
+        <v>473247</v>
       </c>
       <c r="R6" t="n">
-        <v>7046097</v>
+        <v>7045894</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1330,6 +1326,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1347,27 +1348,32 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1385,10 +1391,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121238543</v>
+        <v>121240324</v>
       </c>
       <c r="B7" t="n">
-        <v>79685</v>
+        <v>79724</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1397,25 +1403,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1468,11 +1474,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Fina exemplar av lunglav på en gammal sälg där vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1535,10 +1536,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121238082</v>
+        <v>121244154</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>78607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1551,46 +1552,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473540</v>
+        <v>473456</v>
       </c>
       <c r="R8" t="n">
-        <v>7046097</v>
+        <v>7045981</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1627,7 +1619,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1636,6 +1628,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1646,7 +1639,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1661,12 +1654,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1684,10 +1677,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121241817</v>
+        <v>121238082</v>
       </c>
       <c r="B9" t="n">
-        <v>78604</v>
+        <v>57354</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1700,37 +1693,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473522</v>
+        <v>473540</v>
       </c>
       <c r="R9" t="n">
-        <v>7045984</v>
+        <v>7046097</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1767,7 +1769,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1776,7 +1778,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1787,7 +1788,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1802,12 +1803,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1825,10 +1826,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121241506</v>
+        <v>121246191</v>
       </c>
       <c r="B10" t="n">
-        <v>78340</v>
+        <v>78343</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1868,13 +1869,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473522</v>
+        <v>473595</v>
       </c>
       <c r="R10" t="n">
-        <v>7045984</v>
+        <v>7046005</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1908,7 +1909,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Gott om kolflarnlav på en kolad tallhögstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1941,11 +1942,6 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>En ca 4 meter hög högstubbe.</t>
-        </is>
-      </c>
       <c r="AM10" t="inlineStr">
         <is>
           <t>Branddödat träd</t>
@@ -1953,7 +1949,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris # En ca 4 meter hög högstubbe.</t>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1971,10 +1967,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121247565</v>
+        <v>121246631</v>
       </c>
       <c r="B11" t="n">
-        <v>79685</v>
+        <v>79717</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1983,32 +1979,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -2018,10 +2014,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473680</v>
+        <v>473702</v>
       </c>
       <c r="R11" t="n">
-        <v>7046060</v>
+        <v>7046035</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2056,11 +2052,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Enstaka bålar av lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -2093,17 +2084,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>En grov sälglåga.</t>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2121,10 +2112,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121241235</v>
+        <v>121241506</v>
       </c>
       <c r="B12" t="n">
-        <v>79685</v>
+        <v>78343</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2137,30 +2128,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2168,10 +2155,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473521</v>
+        <v>473522</v>
       </c>
       <c r="R12" t="n">
-        <v>7046016</v>
+        <v>7045984</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2208,7 +2195,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om kolflarnlav på en kolad tallhögstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2228,32 +2215,32 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>En grov sälglåga.</t>
+          <t>En ca 4 meter hög högstubbe.</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris # En ca 4 meter hög högstubbe.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2271,10 +2258,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121246773</v>
+        <v>121246722</v>
       </c>
       <c r="B13" t="n">
-        <v>79685</v>
+        <v>79723</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2283,30 +2270,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2314,10 +2305,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473688</v>
+        <v>473702</v>
       </c>
       <c r="R13" t="n">
-        <v>7046072</v>
+        <v>7046035</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2352,11 +2343,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Enstaka stora bålar av lunglav några meter upp på en grovbarkad sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2387,6 +2373,11 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>En flerstammig sälg.</t>
+        </is>
+      </c>
       <c r="AM13" t="inlineStr">
         <is>
           <t>Bark på levande träd</t>
@@ -2394,7 +2385,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2412,10 +2403,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121247541</v>
+        <v>121231827</v>
       </c>
       <c r="B14" t="n">
-        <v>79721</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2424,34 +2415,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2459,10 +2446,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473680</v>
+        <v>473583</v>
       </c>
       <c r="R14" t="n">
-        <v>7046060</v>
+        <v>7046084</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2497,6 +2484,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2519,27 +2511,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2557,10 +2544,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121242466</v>
+        <v>121238149</v>
       </c>
       <c r="B15" t="n">
-        <v>90728</v>
+        <v>78607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2573,49 +2560,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473518</v>
+        <v>473540</v>
       </c>
       <c r="R15" t="n">
-        <v>7045959</v>
+        <v>7046097</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2652,7 +2627,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2672,7 +2647,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2685,19 +2660,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>En smal död gran som är knäckt vid basen.</t>
-        </is>
-      </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2715,10 +2685,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121247570</v>
+        <v>121246432</v>
       </c>
       <c r="B16" t="n">
-        <v>79686</v>
+        <v>79689</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2762,10 +2732,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473680</v>
+        <v>473702</v>
       </c>
       <c r="R16" t="n">
-        <v>7046060</v>
+        <v>7046035</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2802,7 +2772,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Enstaka bålar av skrovellav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2837,17 +2807,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>En grov sälglåga.</t>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2865,10 +2835,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121246631</v>
+        <v>121246207</v>
       </c>
       <c r="B17" t="n">
-        <v>79714</v>
+        <v>90731</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2877,34 +2847,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2912,13 +2886,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473702</v>
+        <v>473595</v>
       </c>
       <c r="R17" t="n">
-        <v>7046035</v>
+        <v>7046005</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2948,6 +2922,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 8 st fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2967,32 +2946,27 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>En flerstammig sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Horizontal, dead without ground contact # En upplyft lutande stam av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3010,10 +2984,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121246191</v>
+        <v>121244747</v>
       </c>
       <c r="B18" t="n">
-        <v>78340</v>
+        <v>56558</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3026,40 +3000,53 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473595</v>
+        <v>473482</v>
       </c>
       <c r="R18" t="n">
-        <v>7046005</v>
+        <v>7045969</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3093,7 +3080,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3102,7 +3089,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -3113,27 +3099,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Branddödat träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
+          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3151,10 +3117,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121244154</v>
+        <v>121241817</v>
       </c>
       <c r="B19" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3194,10 +3160,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473456</v>
+        <v>473522</v>
       </c>
       <c r="R19" t="n">
-        <v>7045981</v>
+        <v>7045984</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3254,7 +3220,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3292,10 +3258,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121231827</v>
+        <v>121247565</v>
       </c>
       <c r="B20" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3308,26 +3274,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3335,10 +3305,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473583</v>
+        <v>473680</v>
       </c>
       <c r="R20" t="n">
-        <v>7046084</v>
+        <v>7046060</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3375,7 +3345,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Enstaka bålar av lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3400,22 +3370,27 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3433,10 +3408,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121245981</v>
+        <v>121245877</v>
       </c>
       <c r="B21" t="n">
-        <v>90728</v>
+        <v>57370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3449,44 +3424,49 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473515</v>
+        <v>473507</v>
       </c>
       <c r="R21" t="n">
-        <v>7045852</v>
+        <v>7045849</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3520,7 +3500,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3529,7 +3509,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3540,7 +3519,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, båhål (hackspettar) i grov asp, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3555,12 +3534,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies</t>
+          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3578,10 +3557,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121231830</v>
+        <v>121241304</v>
       </c>
       <c r="B22" t="n">
-        <v>78604</v>
+        <v>79717</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3590,30 +3569,34 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3621,10 +3604,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473557</v>
+        <v>473521</v>
       </c>
       <c r="R22" t="n">
-        <v>7046096</v>
+        <v>7046016</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3659,11 +3642,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3686,22 +3664,27 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3719,10 +3702,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121245697</v>
+        <v>121246773</v>
       </c>
       <c r="B23" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3735,21 +3718,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3762,10 +3745,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473293</v>
+        <v>473688</v>
       </c>
       <c r="R23" t="n">
-        <v>7045728</v>
+        <v>7046072</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3802,7 +3785,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Enstaka stora bålar av lunglav några meter upp på en grovbarkad sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3822,27 +3805,27 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3860,10 +3843,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121246207</v>
+        <v>121238339</v>
       </c>
       <c r="B24" t="n">
-        <v>90728</v>
+        <v>91396</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3872,52 +3855,44 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473595</v>
+        <v>473540</v>
       </c>
       <c r="R24" t="n">
-        <v>7046005</v>
+        <v>7046097</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3947,11 +3922,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minst 8 st fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3971,7 +3941,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -3986,12 +3956,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # En upplyft lutande stam av en knäckt gran. # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -4009,10 +3979,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121244830</v>
+        <v>121241235</v>
       </c>
       <c r="B25" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -4025,26 +3995,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -4052,10 +4026,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473247</v>
+        <v>473521</v>
       </c>
       <c r="R25" t="n">
-        <v>7045894</v>
+        <v>7046016</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -4092,7 +4066,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4112,32 +4086,32 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Flera granar.</t>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4155,10 +4129,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121238339</v>
+        <v>121247541</v>
       </c>
       <c r="B26" t="n">
-        <v>91393</v>
+        <v>79724</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4171,37 +4145,41 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473540</v>
+        <v>473680</v>
       </c>
       <c r="R26" t="n">
-        <v>7046097</v>
+        <v>7046060</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4258,22 +4236,27 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4291,10 +4274,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121241286</v>
+        <v>121247570</v>
       </c>
       <c r="B27" t="n">
-        <v>79721</v>
+        <v>79689</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4303,32 +4286,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -4338,10 +4321,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473521</v>
+        <v>473680</v>
       </c>
       <c r="R27" t="n">
-        <v>7046016</v>
+        <v>7046060</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4374,6 +4357,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Enstaka bålar av skrovellav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4436,10 +4424,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121246722</v>
+        <v>121245697</v>
       </c>
       <c r="B28" t="n">
-        <v>79720</v>
+        <v>78607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4448,20 +4436,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4471,11 +4459,7 @@
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4483,10 +4467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473702</v>
+        <v>473293</v>
       </c>
       <c r="R28" t="n">
-        <v>7046035</v>
+        <v>7045728</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4521,6 +4505,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4538,32 +4527,27 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>En flerstammig sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4581,10 +4565,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121245877</v>
+        <v>121238387</v>
       </c>
       <c r="B29" t="n">
-        <v>57367</v>
+        <v>79717</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4593,50 +4577,45 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473507</v>
+        <v>473540</v>
       </c>
       <c r="R29" t="n">
-        <v>7045849</v>
+        <v>7046097</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4671,17 +4650,13 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4692,27 +4667,27 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4730,10 +4705,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121238149</v>
+        <v>121231824</v>
       </c>
       <c r="B30" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4769,14 +4744,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473540</v>
+        <v>473642</v>
       </c>
       <c r="R30" t="n">
-        <v>7046097</v>
+        <v>7046059</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4813,7 +4788,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4871,10 +4846,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121244747</v>
+        <v>121241286</v>
       </c>
       <c r="B31" t="n">
-        <v>56555</v>
+        <v>79724</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4883,57 +4858,48 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473482</v>
+        <v>473521</v>
       </c>
       <c r="R31" t="n">
-        <v>7045969</v>
+        <v>7046016</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4965,17 +4931,13 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4986,7 +4948,32 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -5004,10 +4991,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121246432</v>
+        <v>121231830</v>
       </c>
       <c r="B32" t="n">
-        <v>79686</v>
+        <v>78607</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5020,30 +5007,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -5051,10 +5034,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473702</v>
+        <v>473557</v>
       </c>
       <c r="R32" t="n">
-        <v>7046035</v>
+        <v>7046096</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -5091,7 +5074,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5116,27 +5099,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>En flerstammig sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5154,10 +5132,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121241304</v>
+        <v>121245981</v>
       </c>
       <c r="B33" t="n">
-        <v>79714</v>
+        <v>90731</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5166,32 +5144,32 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -5201,13 +5179,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473521</v>
+        <v>473515</v>
       </c>
       <c r="R33" t="n">
-        <v>7046016</v>
+        <v>7045852</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5237,6 +5215,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5256,32 +5239,27 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, båhål (hackspettar) i grov asp, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5299,10 +5277,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121231824</v>
+        <v>121242466</v>
       </c>
       <c r="B34" t="n">
-        <v>78604</v>
+        <v>90731</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5315,26 +5293,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -5342,10 +5332,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473642</v>
+        <v>473518</v>
       </c>
       <c r="R34" t="n">
-        <v>7046059</v>
+        <v>7045959</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5382,7 +5372,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5402,7 +5392,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -5415,14 +5405,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>En smal död gran som är knäckt vid basen.</t>
+        </is>
+      </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5440,10 +5435,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121240324</v>
+        <v>121238543</v>
       </c>
       <c r="B35" t="n">
-        <v>79721</v>
+        <v>79688</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5452,25 +5447,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5523,6 +5518,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Fina exemplar av lunglav på en gammal sälg där vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5588,7 +5588,7 @@
         <v>121218973</v>
       </c>
       <c r="B36" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>121260476</v>
       </c>
       <c r="B37" t="n">
-        <v>74702</v>
+        <v>74705</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>

--- a/artfynd/A 39937-2024 artfynd.xlsx
+++ b/artfynd/A 39937-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121219351</v>
+        <v>121219127</v>
       </c>
       <c r="B2" t="n">
         <v>98098</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473214</v>
+        <v>473560</v>
       </c>
       <c r="R2" t="n">
-        <v>7045971</v>
+        <v>7046115</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -775,7 +775,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Knärot med minst 33 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -813,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121219127</v>
+        <v>121219221</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
+        <v>57354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,43 +825,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -869,14 +861,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473560</v>
+        <v>473234</v>
       </c>
       <c r="R3" t="n">
-        <v>7046115</v>
+        <v>7045879</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -913,7 +905,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Knärot med minst 33 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om färska ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,7 +914,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -934,6 +925,26 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -951,10 +962,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121219221</v>
+        <v>121219351</v>
       </c>
       <c r="B4" t="n">
-        <v>57354</v>
+        <v>98098</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -963,35 +974,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -999,14 +1018,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473234</v>
+        <v>473214</v>
       </c>
       <c r="R4" t="n">
-        <v>7045879</v>
+        <v>7045971</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1043,7 +1062,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,6 +1071,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1063,26 +1083,6 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121244830</v>
+        <v>121245877</v>
       </c>
       <c r="B6" t="n">
-        <v>78607</v>
+        <v>57370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1261,37 +1261,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473247</v>
+        <v>473507</v>
       </c>
       <c r="R6" t="n">
-        <v>7045894</v>
+        <v>7045849</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1328,7 +1337,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1337,7 +1346,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1348,7 +1356,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1361,19 +1369,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1536,7 +1539,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121244154</v>
+        <v>121245697</v>
       </c>
       <c r="B8" t="n">
         <v>78607</v>
@@ -1579,10 +1582,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473456</v>
+        <v>473293</v>
       </c>
       <c r="R8" t="n">
-        <v>7045981</v>
+        <v>7045728</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1639,7 +1642,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1677,10 +1680,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121238082</v>
+        <v>121241506</v>
       </c>
       <c r="B9" t="n">
-        <v>57354</v>
+        <v>78343</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1693,46 +1696,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473540</v>
+        <v>473522</v>
       </c>
       <c r="R9" t="n">
-        <v>7046097</v>
+        <v>7045984</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1769,7 +1763,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om kolflarnlav på en kolad tallhögstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1778,6 +1772,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1788,27 +1783,32 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>En ca 4 meter hög högstubbe.</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris # En ca 4 meter hög högstubbe.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1826,10 +1826,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246191</v>
+        <v>121241235</v>
       </c>
       <c r="B10" t="n">
-        <v>78343</v>
+        <v>79688</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1842,26 +1842,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1869,13 +1873,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473595</v>
+        <v>473521</v>
       </c>
       <c r="R10" t="n">
-        <v>7046005</v>
+        <v>7046016</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1909,7 +1913,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1929,27 +1933,32 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1967,10 +1976,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121246631</v>
+        <v>121244747</v>
       </c>
       <c r="B11" t="n">
-        <v>79717</v>
+        <v>56558</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1979,48 +1988,57 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473702</v>
+        <v>473482</v>
       </c>
       <c r="R11" t="n">
-        <v>7046035</v>
+        <v>7045969</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2052,13 +2070,17 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2069,32 +2091,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>En flerstammig sälg.</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2112,10 +2109,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121241506</v>
+        <v>121231827</v>
       </c>
       <c r="B12" t="n">
-        <v>78343</v>
+        <v>78607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2128,21 +2125,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2155,10 +2152,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473522</v>
+        <v>473583</v>
       </c>
       <c r="R12" t="n">
-        <v>7045984</v>
+        <v>7046084</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2195,7 +2192,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gott om kolflarnlav på en kolad tallhögstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2215,32 +2212,27 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>En ca 4 meter hög högstubbe.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris # En ca 4 meter hög högstubbe.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2258,10 +2250,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121246722</v>
+        <v>121246191</v>
       </c>
       <c r="B13" t="n">
-        <v>79723</v>
+        <v>78343</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2270,34 +2262,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2305,13 +2293,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473702</v>
+        <v>473595</v>
       </c>
       <c r="R13" t="n">
-        <v>7046035</v>
+        <v>7046005</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2341,6 +2329,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2360,32 +2353,27 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>En flerstammig sälg.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2403,10 +2391,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121231827</v>
+        <v>121242466</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>90731</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2419,26 +2407,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473583</v>
+        <v>473518</v>
       </c>
       <c r="R14" t="n">
-        <v>7046084</v>
+        <v>7045959</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2519,14 +2519,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>En smal död gran som är knäckt vid basen.</t>
+        </is>
+      </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2544,10 +2549,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121238149</v>
+        <v>121246207</v>
       </c>
       <c r="B15" t="n">
-        <v>78607</v>
+        <v>90731</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2560,40 +2565,48 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473540</v>
+        <v>473595</v>
       </c>
       <c r="R15" t="n">
-        <v>7046097</v>
+        <v>7046005</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2627,7 +2640,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Minst 8 st fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2647,7 +2660,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2662,12 +2675,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # En upplyft lutande stam av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2685,10 +2698,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121246432</v>
+        <v>121245981</v>
       </c>
       <c r="B16" t="n">
-        <v>79689</v>
+        <v>90731</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2701,28 +2714,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2732,13 +2745,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473702</v>
+        <v>473515</v>
       </c>
       <c r="R16" t="n">
-        <v>7046035</v>
+        <v>7045852</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2772,7 +2785,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2792,32 +2805,27 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, båhål (hackspettar) i grov asp, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>En flerstammig sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2835,10 +2843,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121246207</v>
+        <v>121241286</v>
       </c>
       <c r="B17" t="n">
-        <v>90731</v>
+        <v>79724</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2847,38 +2855,34 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2886,13 +2890,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473595</v>
+        <v>473521</v>
       </c>
       <c r="R17" t="n">
-        <v>7046005</v>
+        <v>7046016</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2922,11 +2926,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Minst 8 st fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2946,27 +2945,32 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # En upplyft lutande stam av en knäckt gran. # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2984,10 +2988,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121244747</v>
+        <v>121244830</v>
       </c>
       <c r="B18" t="n">
-        <v>56558</v>
+        <v>78607</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3000,53 +3004,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473482</v>
+        <v>473247</v>
       </c>
       <c r="R18" t="n">
-        <v>7045969</v>
+        <v>7045894</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3080,7 +3071,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3089,6 +3080,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -3099,7 +3091,32 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3117,7 +3134,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121241817</v>
+        <v>121244154</v>
       </c>
       <c r="B19" t="n">
         <v>78607</v>
@@ -3160,10 +3177,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473522</v>
+        <v>473456</v>
       </c>
       <c r="R19" t="n">
-        <v>7045984</v>
+        <v>7045981</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3220,7 +3237,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3258,10 +3275,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121247565</v>
+        <v>121241304</v>
       </c>
       <c r="B20" t="n">
-        <v>79688</v>
+        <v>79717</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3270,32 +3287,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3305,10 +3322,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473680</v>
+        <v>473521</v>
       </c>
       <c r="R20" t="n">
-        <v>7046060</v>
+        <v>7046016</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3341,11 +3358,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Enstaka bålar av lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3408,10 +3420,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121245877</v>
+        <v>121238149</v>
       </c>
       <c r="B21" t="n">
-        <v>57370</v>
+        <v>78607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3424,46 +3436,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473507</v>
+        <v>473540</v>
       </c>
       <c r="R21" t="n">
-        <v>7045849</v>
+        <v>7046097</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3500,7 +3503,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3509,6 +3512,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3519,7 +3523,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3534,12 +3538,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3557,10 +3561,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121241304</v>
+        <v>121238543</v>
       </c>
       <c r="B22" t="n">
-        <v>79717</v>
+        <v>79688</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3569,25 +3573,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3604,10 +3608,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473521</v>
+        <v>473527</v>
       </c>
       <c r="R22" t="n">
-        <v>7046016</v>
+        <v>7046057</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3642,6 +3646,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Fina exemplar av lunglav på en gammal sälg där vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3674,17 +3683,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>En grov sälglåga.</t>
+          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3702,10 +3711,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121246773</v>
+        <v>121246432</v>
       </c>
       <c r="B23" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3718,26 +3727,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3745,10 +3758,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473688</v>
+        <v>473702</v>
       </c>
       <c r="R23" t="n">
-        <v>7046072</v>
+        <v>7046035</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3785,7 +3798,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Enstaka stora bålar av lunglav några meter upp på en grovbarkad sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3818,6 +3831,11 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>En flerstammig sälg.</t>
+        </is>
+      </c>
       <c r="AM23" t="inlineStr">
         <is>
           <t>Bark på levande träd</t>
@@ -3825,7 +3843,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3843,10 +3861,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121238339</v>
+        <v>121246631</v>
       </c>
       <c r="B24" t="n">
-        <v>91396</v>
+        <v>79717</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3859,37 +3877,41 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473540</v>
+        <v>473702</v>
       </c>
       <c r="R24" t="n">
-        <v>7046097</v>
+        <v>7046035</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3946,22 +3968,27 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3979,10 +4006,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121241235</v>
+        <v>121247570</v>
       </c>
       <c r="B25" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3995,21 +4022,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -4026,10 +4053,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473521</v>
+        <v>473680</v>
       </c>
       <c r="R25" t="n">
-        <v>7046016</v>
+        <v>7046060</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -4066,7 +4093,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Enstaka bålar av skrovellav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4129,10 +4156,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121247541</v>
+        <v>121246773</v>
       </c>
       <c r="B26" t="n">
-        <v>79724</v>
+        <v>79688</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4141,34 +4168,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -4176,10 +4199,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473680</v>
+        <v>473688</v>
       </c>
       <c r="R26" t="n">
-        <v>7046060</v>
+        <v>7046072</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4214,6 +4237,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Enstaka stora bålar av lunglav några meter upp på en grovbarkad sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -4244,19 +4272,14 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
-        </is>
-      </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4274,10 +4297,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121247570</v>
+        <v>121241817</v>
       </c>
       <c r="B27" t="n">
-        <v>79689</v>
+        <v>78607</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4290,30 +4313,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4321,10 +4340,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473680</v>
+        <v>473522</v>
       </c>
       <c r="R27" t="n">
-        <v>7046060</v>
+        <v>7045984</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4361,7 +4380,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Enstaka bålar av skrovellav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4381,32 +4400,27 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4424,10 +4438,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121245697</v>
+        <v>121238387</v>
       </c>
       <c r="B28" t="n">
-        <v>78607</v>
+        <v>79717</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4436,41 +4450,45 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473293</v>
+        <v>473540</v>
       </c>
       <c r="R28" t="n">
-        <v>7045728</v>
+        <v>7046097</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4505,11 +4523,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4527,27 +4540,27 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4565,10 +4578,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121238387</v>
+        <v>121231824</v>
       </c>
       <c r="B29" t="n">
-        <v>79717</v>
+        <v>78607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4577,45 +4590,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473540</v>
+        <v>473642</v>
       </c>
       <c r="R29" t="n">
-        <v>7046097</v>
+        <v>7046059</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4650,6 +4659,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4672,22 +4686,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4705,7 +4719,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121231824</v>
+        <v>121231830</v>
       </c>
       <c r="B30" t="n">
         <v>78607</v>
@@ -4748,10 +4762,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473642</v>
+        <v>473557</v>
       </c>
       <c r="R30" t="n">
-        <v>7046059</v>
+        <v>7046096</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4846,7 +4860,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121241286</v>
+        <v>121247541</v>
       </c>
       <c r="B31" t="n">
         <v>79724</v>
@@ -4893,10 +4907,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473521</v>
+        <v>473680</v>
       </c>
       <c r="R31" t="n">
-        <v>7046016</v>
+        <v>7046060</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4991,10 +5005,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121231830</v>
+        <v>121247565</v>
       </c>
       <c r="B32" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5007,26 +5021,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -5034,10 +5052,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473557</v>
+        <v>473680</v>
       </c>
       <c r="R32" t="n">
-        <v>7046096</v>
+        <v>7046060</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -5074,7 +5092,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Enstaka bålar av lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5099,22 +5117,27 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5132,10 +5155,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121245981</v>
+        <v>121238082</v>
       </c>
       <c r="B33" t="n">
-        <v>90731</v>
+        <v>57354</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5148,44 +5171,49 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473515</v>
+        <v>473540</v>
       </c>
       <c r="R33" t="n">
-        <v>7045852</v>
+        <v>7046097</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5228,7 +5256,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -5239,7 +5266,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, båhål (hackspettar) i grov asp, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -5254,12 +5281,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5277,10 +5304,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121242466</v>
+        <v>121238339</v>
       </c>
       <c r="B34" t="n">
-        <v>90731</v>
+        <v>91396</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5289,53 +5316,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473518</v>
+        <v>473540</v>
       </c>
       <c r="R34" t="n">
-        <v>7045959</v>
+        <v>7046097</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5370,11 +5385,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -5392,7 +5402,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -5405,19 +5415,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>En smal död gran som är knäckt vid basen.</t>
-        </is>
-      </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5435,10 +5440,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121238543</v>
+        <v>121246722</v>
       </c>
       <c r="B35" t="n">
-        <v>79688</v>
+        <v>79723</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5447,32 +5452,32 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -5482,10 +5487,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473527</v>
+        <v>473702</v>
       </c>
       <c r="R35" t="n">
-        <v>7046057</v>
+        <v>7046035</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5520,11 +5525,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Fina exemplar av lunglav på en gammal sälg där vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121218973</v>
+        <v>121260476</v>
       </c>
       <c r="B36" t="n">
-        <v>90713</v>
+        <v>74705</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5601,21 +5601,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5628,13 +5628,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473506</v>
+        <v>473489</v>
       </c>
       <c r="R36" t="n">
-        <v>7046084</v>
+        <v>7046095</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5693,22 +5693,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Wood surface of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5726,10 +5726,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121260476</v>
+        <v>121218973</v>
       </c>
       <c r="B37" t="n">
-        <v>74705</v>
+        <v>90713</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5742,21 +5742,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5769,13 +5769,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473489</v>
+        <v>473506</v>
       </c>
       <c r="R37" t="n">
-        <v>7046095</v>
+        <v>7046084</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5834,22 +5834,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Betula</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>

--- a/artfynd/A 39937-2024 artfynd.xlsx
+++ b/artfynd/A 39937-2024 artfynd.xlsx
@@ -3275,10 +3275,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121241304</v>
+        <v>121238149</v>
       </c>
       <c r="B20" t="n">
-        <v>79717</v>
+        <v>78607</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3287,45 +3287,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473521</v>
+        <v>473540</v>
       </c>
       <c r="R20" t="n">
-        <v>7046016</v>
+        <v>7046097</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3360,6 +3356,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3382,27 +3383,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3420,10 +3416,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121238149</v>
+        <v>121241304</v>
       </c>
       <c r="B21" t="n">
-        <v>78607</v>
+        <v>79717</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3432,41 +3428,45 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473540</v>
+        <v>473521</v>
       </c>
       <c r="R21" t="n">
-        <v>7046097</v>
+        <v>7046016</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3501,11 +3501,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3528,22 +3523,27 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>

--- a/artfynd/A 39937-2024 artfynd.xlsx
+++ b/artfynd/A 39937-2024 artfynd.xlsx
@@ -1245,10 +1245,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121245877</v>
+        <v>121240324</v>
       </c>
       <c r="B6" t="n">
-        <v>57370</v>
+        <v>79724</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1257,50 +1257,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473507</v>
+        <v>473527</v>
       </c>
       <c r="R6" t="n">
-        <v>7045849</v>
+        <v>7046057</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1335,17 +1330,13 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1356,27 +1347,32 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1394,10 +1390,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121240324</v>
+        <v>121245877</v>
       </c>
       <c r="B7" t="n">
-        <v>79724</v>
+        <v>57370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1406,45 +1402,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473527</v>
+        <v>473507</v>
       </c>
       <c r="R7" t="n">
-        <v>7046057</v>
+        <v>7045849</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1479,13 +1480,17 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1496,32 +1501,27 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -2109,10 +2109,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121231827</v>
+        <v>121246191</v>
       </c>
       <c r="B12" t="n">
-        <v>78607</v>
+        <v>78343</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2125,21 +2125,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2152,13 +2152,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473583</v>
+        <v>473595</v>
       </c>
       <c r="R12" t="n">
-        <v>7046084</v>
+        <v>7046005</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2212,27 +2212,27 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121246191</v>
+        <v>121231827</v>
       </c>
       <c r="B13" t="n">
-        <v>78343</v>
+        <v>78607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2266,21 +2266,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2293,13 +2293,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473595</v>
+        <v>473583</v>
       </c>
       <c r="R13" t="n">
-        <v>7046005</v>
+        <v>7046084</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2353,27 +2353,27 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121238149</v>
+        <v>121241304</v>
       </c>
       <c r="B20" t="n">
-        <v>78607</v>
+        <v>79717</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3287,41 +3287,45 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473540</v>
+        <v>473521</v>
       </c>
       <c r="R20" t="n">
-        <v>7046097</v>
+        <v>7046016</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3356,11 +3360,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3383,22 +3382,27 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3416,10 +3420,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121241304</v>
+        <v>121238149</v>
       </c>
       <c r="B21" t="n">
-        <v>79717</v>
+        <v>78607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3428,45 +3432,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473521</v>
+        <v>473540</v>
       </c>
       <c r="R21" t="n">
-        <v>7046016</v>
+        <v>7046097</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3501,6 +3501,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3523,27 +3528,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121246631</v>
+        <v>121247570</v>
       </c>
       <c r="B24" t="n">
-        <v>79717</v>
+        <v>79689</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3873,32 +3873,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473702</v>
+        <v>473680</v>
       </c>
       <c r="R24" t="n">
-        <v>7046035</v>
+        <v>7046060</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3946,6 +3946,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Enstaka bålar av skrovellav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3978,17 +3983,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>En flerstammig sälg.</t>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -4006,10 +4011,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121247570</v>
+        <v>121246631</v>
       </c>
       <c r="B25" t="n">
-        <v>79689</v>
+        <v>79717</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -4018,32 +4023,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -4053,10 +4058,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473680</v>
+        <v>473702</v>
       </c>
       <c r="R25" t="n">
-        <v>7046060</v>
+        <v>7046035</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -4091,11 +4096,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Enstaka bålar av skrovellav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -4128,17 +4128,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>En grov sälglåga.</t>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -5304,10 +5304,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121238339</v>
+        <v>121246722</v>
       </c>
       <c r="B34" t="n">
-        <v>91396</v>
+        <v>79723</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5320,37 +5320,41 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473540</v>
+        <v>473702</v>
       </c>
       <c r="R34" t="n">
-        <v>7046097</v>
+        <v>7046035</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5407,22 +5411,27 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5440,10 +5449,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121246722</v>
+        <v>121238339</v>
       </c>
       <c r="B35" t="n">
-        <v>79723</v>
+        <v>91396</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5456,41 +5465,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6463</v>
+        <v>3298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473702</v>
+        <v>473540</v>
       </c>
       <c r="R35" t="n">
-        <v>7046035</v>
+        <v>7046097</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5547,27 +5552,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>En flerstammig sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>

--- a/artfynd/A 39937-2024 artfynd.xlsx
+++ b/artfynd/A 39937-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121219127</v>
+        <v>121219351</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473560</v>
+        <v>473214</v>
       </c>
       <c r="R2" t="n">
-        <v>7046115</v>
+        <v>7045971</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -775,7 +775,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Knärot med minst 33 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -816,7 +816,7 @@
         <v>121219221</v>
       </c>
       <c r="B3" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -962,10 +962,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121219351</v>
+        <v>121219127</v>
       </c>
       <c r="B4" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1022,10 +1022,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473214</v>
+        <v>473560</v>
       </c>
       <c r="R4" t="n">
-        <v>7045971</v>
+        <v>7046115</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Knärot med minst 33 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1103,7 +1103,7 @@
         <v>121219485</v>
       </c>
       <c r="B5" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121240324</v>
+        <v>121238543</v>
       </c>
       <c r="B6" t="n">
-        <v>79724</v>
+        <v>79689</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1257,25 +1257,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1328,6 +1328,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Fina exemplar av lunglav på en gammal sälg där vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1390,10 +1395,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121245877</v>
+        <v>121246722</v>
       </c>
       <c r="B7" t="n">
-        <v>57370</v>
+        <v>79724</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1402,50 +1407,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473507</v>
+        <v>473702</v>
       </c>
       <c r="R7" t="n">
-        <v>7045849</v>
+        <v>7046035</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1480,17 +1480,13 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1501,27 +1497,32 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1539,10 +1540,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121245697</v>
+        <v>121244154</v>
       </c>
       <c r="B8" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1582,10 +1583,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473293</v>
+        <v>473456</v>
       </c>
       <c r="R8" t="n">
-        <v>7045728</v>
+        <v>7045981</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1642,7 +1643,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1680,10 +1681,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121241506</v>
+        <v>121246191</v>
       </c>
       <c r="B9" t="n">
-        <v>78343</v>
+        <v>78344</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1723,13 +1724,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473522</v>
+        <v>473595</v>
       </c>
       <c r="R9" t="n">
-        <v>7045984</v>
+        <v>7046005</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1763,7 +1764,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gott om kolflarnlav på en kolad tallhögstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1796,11 +1797,6 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>En ca 4 meter hög högstubbe.</t>
-        </is>
-      </c>
       <c r="AM9" t="inlineStr">
         <is>
           <t>Branddödat träd</t>
@@ -1808,7 +1804,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris # En ca 4 meter hög högstubbe.</t>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1826,10 +1822,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121241235</v>
+        <v>121246631</v>
       </c>
       <c r="B10" t="n">
-        <v>79688</v>
+        <v>79718</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1838,32 +1834,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1873,10 +1869,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473521</v>
+        <v>473702</v>
       </c>
       <c r="R10" t="n">
-        <v>7046016</v>
+        <v>7046035</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1911,11 +1907,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1948,17 +1939,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>En grov sälglåga.</t>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1976,10 +1967,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121244747</v>
+        <v>121231827</v>
       </c>
       <c r="B11" t="n">
-        <v>56558</v>
+        <v>78608</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1992,53 +1983,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473482</v>
+        <v>473583</v>
       </c>
       <c r="R11" t="n">
-        <v>7045969</v>
+        <v>7046084</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2072,7 +2050,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2081,6 +2059,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2091,7 +2070,27 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2109,10 +2108,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121246191</v>
+        <v>121238149</v>
       </c>
       <c r="B12" t="n">
-        <v>78343</v>
+        <v>78608</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2125,21 +2124,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2148,17 +2147,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473595</v>
+        <v>473540</v>
       </c>
       <c r="R12" t="n">
-        <v>7046005</v>
+        <v>7046097</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2192,7 +2191,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2212,27 +2211,27 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2250,10 +2249,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121231827</v>
+        <v>121241286</v>
       </c>
       <c r="B13" t="n">
-        <v>78607</v>
+        <v>79725</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2262,30 +2261,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2293,10 +2296,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473583</v>
+        <v>473521</v>
       </c>
       <c r="R13" t="n">
-        <v>7046084</v>
+        <v>7046016</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2331,11 +2334,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2358,22 +2356,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2391,10 +2394,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121242466</v>
+        <v>121238339</v>
       </c>
       <c r="B14" t="n">
-        <v>90731</v>
+        <v>91402</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2403,53 +2406,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473518</v>
+        <v>473540</v>
       </c>
       <c r="R14" t="n">
-        <v>7045959</v>
+        <v>7046097</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2484,11 +2475,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2506,7 +2492,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2519,19 +2505,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>En smal död gran som är knäckt vid basen.</t>
-        </is>
-      </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2549,10 +2530,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121246207</v>
+        <v>121241817</v>
       </c>
       <c r="B15" t="n">
-        <v>90731</v>
+        <v>78608</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2565,33 +2546,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2600,13 +2573,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473595</v>
+        <v>473522</v>
       </c>
       <c r="R15" t="n">
-        <v>7046005</v>
+        <v>7045984</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2640,7 +2613,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 8 st fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2675,12 +2648,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # En upplyft lutande stam av en knäckt gran. # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2701,7 +2674,7 @@
         <v>121245981</v>
       </c>
       <c r="B16" t="n">
-        <v>90731</v>
+        <v>90737</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2843,10 +2816,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121241286</v>
+        <v>121238387</v>
       </c>
       <c r="B17" t="n">
-        <v>79724</v>
+        <v>79718</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2859,21 +2832,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2886,14 +2859,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473521</v>
+        <v>473540</v>
       </c>
       <c r="R17" t="n">
-        <v>7046016</v>
+        <v>7046097</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2958,19 +2931,14 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
-        </is>
-      </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2988,10 +2956,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121244830</v>
+        <v>121241235</v>
       </c>
       <c r="B18" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3004,26 +2972,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -3031,10 +3003,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473247</v>
+        <v>473521</v>
       </c>
       <c r="R18" t="n">
-        <v>7045894</v>
+        <v>7046016</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3071,7 +3043,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3091,32 +3063,32 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Flera granar.</t>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3134,10 +3106,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121244154</v>
+        <v>121242466</v>
       </c>
       <c r="B19" t="n">
-        <v>78607</v>
+        <v>90737</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3150,26 +3122,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3177,10 +3161,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473456</v>
+        <v>473518</v>
       </c>
       <c r="R19" t="n">
-        <v>7045981</v>
+        <v>7045959</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3217,7 +3201,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3237,7 +3221,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3250,14 +3234,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>En smal död gran som är knäckt vid basen.</t>
+        </is>
+      </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3275,10 +3264,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121241304</v>
+        <v>121247541</v>
       </c>
       <c r="B20" t="n">
-        <v>79717</v>
+        <v>79725</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3291,21 +3280,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3322,10 +3311,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473521</v>
+        <v>473680</v>
       </c>
       <c r="R20" t="n">
-        <v>7046016</v>
+        <v>7046060</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3420,10 +3409,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121238149</v>
+        <v>121246432</v>
       </c>
       <c r="B21" t="n">
-        <v>78607</v>
+        <v>79690</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3436,37 +3425,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473540</v>
+        <v>473702</v>
       </c>
       <c r="R21" t="n">
-        <v>7046097</v>
+        <v>7046035</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3503,7 +3496,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3528,22 +3521,27 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3561,10 +3559,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121238543</v>
+        <v>121231830</v>
       </c>
       <c r="B22" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3577,30 +3575,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3608,10 +3602,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473527</v>
+        <v>473557</v>
       </c>
       <c r="R22" t="n">
-        <v>7046057</v>
+        <v>7046096</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3648,7 +3642,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Fina exemplar av lunglav på en gammal sälg där vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3673,27 +3667,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3711,10 +3700,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121246432</v>
+        <v>121231824</v>
       </c>
       <c r="B23" t="n">
-        <v>79689</v>
+        <v>78608</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3727,30 +3716,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3758,10 +3743,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473702</v>
+        <v>473642</v>
       </c>
       <c r="R23" t="n">
-        <v>7046035</v>
+        <v>7046059</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3798,7 +3783,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3823,27 +3808,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>En flerstammig sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3861,10 +3841,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121247570</v>
+        <v>121238082</v>
       </c>
       <c r="B24" t="n">
-        <v>79689</v>
+        <v>57355</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3877,41 +3857,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473680</v>
+        <v>473540</v>
       </c>
       <c r="R24" t="n">
-        <v>7046060</v>
+        <v>7046097</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3948,7 +3933,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Enstaka bålar av skrovellav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3957,7 +3942,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3973,27 +3957,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -4011,10 +3990,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121246631</v>
+        <v>121244747</v>
       </c>
       <c r="B25" t="n">
-        <v>79717</v>
+        <v>56559</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -4023,48 +4002,57 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473702</v>
+        <v>473482</v>
       </c>
       <c r="R25" t="n">
-        <v>7046035</v>
+        <v>7045969</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -4096,13 +4084,17 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -4113,32 +4105,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>En flerstammig sälg.</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4156,10 +4123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121246773</v>
+        <v>121245697</v>
       </c>
       <c r="B26" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4172,21 +4139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -4199,10 +4166,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473688</v>
+        <v>473293</v>
       </c>
       <c r="R26" t="n">
-        <v>7046072</v>
+        <v>7045728</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4239,7 +4206,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Enstaka stora bålar av lunglav några meter upp på en grovbarkad sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4259,27 +4226,27 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4297,10 +4264,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121241817</v>
+        <v>121240324</v>
       </c>
       <c r="B27" t="n">
-        <v>78607</v>
+        <v>79725</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4309,30 +4276,34 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4340,10 +4311,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473522</v>
+        <v>473527</v>
       </c>
       <c r="R27" t="n">
-        <v>7045984</v>
+        <v>7046057</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4378,11 +4349,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4400,27 +4366,32 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4438,10 +4409,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121238387</v>
+        <v>121246207</v>
       </c>
       <c r="B28" t="n">
-        <v>79717</v>
+        <v>90737</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4450,48 +4421,52 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473540</v>
+        <v>473595</v>
       </c>
       <c r="R28" t="n">
-        <v>7046097</v>
+        <v>7046005</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4521,6 +4496,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Minst 8 st fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4540,27 +4520,27 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # En upplyft lutande stam av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4578,10 +4558,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121231824</v>
+        <v>121241304</v>
       </c>
       <c r="B29" t="n">
-        <v>78607</v>
+        <v>79718</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4590,30 +4570,34 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4621,10 +4605,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473642</v>
+        <v>473521</v>
       </c>
       <c r="R29" t="n">
-        <v>7046059</v>
+        <v>7046016</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4659,11 +4643,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4686,22 +4665,27 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4719,10 +4703,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121231830</v>
+        <v>121244830</v>
       </c>
       <c r="B30" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4762,10 +4746,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473557</v>
+        <v>473247</v>
       </c>
       <c r="R30" t="n">
-        <v>7046096</v>
+        <v>7045894</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4802,7 +4786,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4822,7 +4806,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4835,6 +4819,11 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
       <c r="AM30" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -4842,7 +4831,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4860,10 +4849,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121247541</v>
+        <v>121247570</v>
       </c>
       <c r="B31" t="n">
-        <v>79724</v>
+        <v>79690</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4872,32 +4861,32 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4943,6 +4932,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Enstaka bålar av skrovellav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -5005,10 +4999,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121247565</v>
+        <v>121245877</v>
       </c>
       <c r="B32" t="n">
-        <v>79688</v>
+        <v>57371</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5021,41 +5015,46 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473680</v>
+        <v>473507</v>
       </c>
       <c r="R32" t="n">
-        <v>7046060</v>
+        <v>7045849</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -5092,7 +5091,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5101,7 +5100,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -5112,32 +5110,27 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5155,10 +5148,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121238082</v>
+        <v>121241506</v>
       </c>
       <c r="B33" t="n">
-        <v>57354</v>
+        <v>78344</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5171,46 +5164,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473540</v>
+        <v>473522</v>
       </c>
       <c r="R33" t="n">
-        <v>7046097</v>
+        <v>7045984</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5247,7 +5231,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om kolflarnlav på en kolad tallhögstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5256,6 +5240,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -5266,27 +5251,32 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>En ca 4 meter hög högstubbe.</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris # En ca 4 meter hög högstubbe.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5304,10 +5294,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121246722</v>
+        <v>121247565</v>
       </c>
       <c r="B34" t="n">
-        <v>79723</v>
+        <v>79689</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5316,25 +5306,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -5351,10 +5341,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473702</v>
+        <v>473680</v>
       </c>
       <c r="R34" t="n">
-        <v>7046035</v>
+        <v>7046060</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5389,6 +5379,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Enstaka bålar av lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -5421,17 +5416,17 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>En flerstammig sälg.</t>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5449,10 +5444,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121238339</v>
+        <v>121246773</v>
       </c>
       <c r="B35" t="n">
-        <v>91396</v>
+        <v>79689</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5461,25 +5456,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5488,14 +5483,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473540</v>
+        <v>473688</v>
       </c>
       <c r="R35" t="n">
-        <v>7046097</v>
+        <v>7046072</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5530,6 +5525,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Enstaka stora bålar av lunglav några meter upp på en grovbarkad sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5552,22 +5552,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121260476</v>
+        <v>121218973</v>
       </c>
       <c r="B36" t="n">
-        <v>74705</v>
+        <v>90719</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5601,21 +5601,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5628,13 +5628,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473489</v>
+        <v>473506</v>
       </c>
       <c r="R36" t="n">
-        <v>7046095</v>
+        <v>7046084</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5693,22 +5693,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Betula</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5726,10 +5726,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121218973</v>
+        <v>121260476</v>
       </c>
       <c r="B37" t="n">
-        <v>90713</v>
+        <v>74706</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5742,21 +5742,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5769,13 +5769,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473506</v>
+        <v>473489</v>
       </c>
       <c r="R37" t="n">
-        <v>7046084</v>
+        <v>7046095</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5834,22 +5834,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Wood surface of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>

--- a/artfynd/A 39937-2024 artfynd.xlsx
+++ b/artfynd/A 39937-2024 artfynd.xlsx
@@ -3106,10 +3106,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121242466</v>
+        <v>121247541</v>
       </c>
       <c r="B19" t="n">
-        <v>90737</v>
+        <v>79725</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3118,40 +3118,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -3161,10 +3153,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473518</v>
+        <v>473680</v>
       </c>
       <c r="R19" t="n">
-        <v>7045959</v>
+        <v>7046060</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3199,11 +3191,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3221,32 +3208,32 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>En smal död gran som är knäckt vid basen.</t>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3264,10 +3251,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121247541</v>
+        <v>121242466</v>
       </c>
       <c r="B20" t="n">
-        <v>79725</v>
+        <v>90737</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3276,32 +3263,40 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3311,10 +3306,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473680</v>
+        <v>473518</v>
       </c>
       <c r="R20" t="n">
-        <v>7046060</v>
+        <v>7045959</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3349,6 +3344,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3366,32 +3366,32 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>En grov sälglåga.</t>
+          <t>En smal död gran som är knäckt vid basen.</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3559,10 +3559,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121231830</v>
+        <v>121238082</v>
       </c>
       <c r="B22" t="n">
-        <v>78608</v>
+        <v>57355</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3575,37 +3575,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473557</v>
+        <v>473540</v>
       </c>
       <c r="R22" t="n">
-        <v>7046096</v>
+        <v>7046097</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3642,7 +3651,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3651,7 +3660,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3677,12 +3685,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3700,7 +3708,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121231824</v>
+        <v>121231830</v>
       </c>
       <c r="B23" t="n">
         <v>78608</v>
@@ -3743,10 +3751,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473642</v>
+        <v>473557</v>
       </c>
       <c r="R23" t="n">
-        <v>7046059</v>
+        <v>7046096</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3841,10 +3849,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121238082</v>
+        <v>121231824</v>
       </c>
       <c r="B24" t="n">
-        <v>57355</v>
+        <v>78608</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3857,46 +3865,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473540</v>
+        <v>473642</v>
       </c>
       <c r="R24" t="n">
-        <v>7046097</v>
+        <v>7046059</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3933,7 +3932,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3942,6 +3941,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3967,12 +3967,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 39937-2024 artfynd.xlsx
+++ b/artfynd/A 39937-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121219351</v>
+        <v>121219485</v>
       </c>
       <c r="B2" t="n">
-        <v>98104</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,58 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473214</v>
+        <v>473631</v>
       </c>
       <c r="R2" t="n">
-        <v>7045971</v>
+        <v>7045992</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -775,7 +763,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Äldre ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +772,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,6 +783,26 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -813,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121219221</v>
+        <v>121219127</v>
       </c>
       <c r="B3" t="n">
-        <v>57355</v>
+        <v>98105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,35 +832,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -861,14 +876,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473234</v>
+        <v>473560</v>
       </c>
       <c r="R3" t="n">
-        <v>7045879</v>
+        <v>7046115</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -905,7 +920,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Knärot med minst 33 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,6 +929,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -925,26 +941,6 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -962,10 +958,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121219127</v>
+        <v>121219351</v>
       </c>
       <c r="B4" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -997,7 +993,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1022,10 +1018,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473560</v>
+        <v>473214</v>
       </c>
       <c r="R4" t="n">
-        <v>7046115</v>
+        <v>7045971</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1062,7 +1058,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Knärot med minst 33 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1100,10 +1096,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121219485</v>
+        <v>121219221</v>
       </c>
       <c r="B5" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1138,20 +1134,24 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473631</v>
+        <v>473234</v>
       </c>
       <c r="R5" t="n">
-        <v>7045992</v>
+        <v>7045879</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om färska ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121238543</v>
+        <v>121241286</v>
       </c>
       <c r="B6" t="n">
-        <v>79689</v>
+        <v>79726</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1257,25 +1257,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473527</v>
+        <v>473521</v>
       </c>
       <c r="R6" t="n">
-        <v>7046057</v>
+        <v>7046016</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1330,11 +1330,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Fina exemplar av lunglav på en gammal sälg där vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1367,17 +1362,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1395,10 +1390,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121246722</v>
+        <v>121241506</v>
       </c>
       <c r="B7" t="n">
-        <v>79724</v>
+        <v>78345</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1407,34 +1402,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1442,10 +1433,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473702</v>
+        <v>473522</v>
       </c>
       <c r="R7" t="n">
-        <v>7046035</v>
+        <v>7045984</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1480,6 +1471,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gott om kolflarnlav på en kolad tallhögstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1497,32 +1493,32 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>En flerstammig sälg.</t>
+          <t>En ca 4 meter hög högstubbe.</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris # En ca 4 meter hög högstubbe.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1540,10 +1536,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121244154</v>
+        <v>121246722</v>
       </c>
       <c r="B8" t="n">
-        <v>78608</v>
+        <v>79725</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1552,20 +1548,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1575,7 +1571,11 @@
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473456</v>
+        <v>473702</v>
       </c>
       <c r="R8" t="n">
-        <v>7045981</v>
+        <v>7046035</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1621,11 +1621,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1643,27 +1638,32 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1681,10 +1681,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121246191</v>
+        <v>121246207</v>
       </c>
       <c r="B9" t="n">
-        <v>78344</v>
+        <v>90738</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1697,25 +1697,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1764,7 +1772,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Minst 8 st fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1789,22 +1797,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
+          <t>Horizontal, dead without ground contact # En upplyft lutande stam av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1822,10 +1830,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246631</v>
+        <v>121247570</v>
       </c>
       <c r="B10" t="n">
-        <v>79718</v>
+        <v>79691</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1834,32 +1842,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1869,10 +1877,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473702</v>
+        <v>473680</v>
       </c>
       <c r="R10" t="n">
-        <v>7046035</v>
+        <v>7046060</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1907,6 +1915,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Enstaka bålar av skrovellav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1939,17 +1952,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>En flerstammig sälg.</t>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1967,10 +1980,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121231827</v>
+        <v>121238387</v>
       </c>
       <c r="B11" t="n">
-        <v>78608</v>
+        <v>79719</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1979,41 +1992,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473583</v>
+        <v>473540</v>
       </c>
       <c r="R11" t="n">
-        <v>7046084</v>
+        <v>7046097</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2048,11 +2065,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -2075,22 +2087,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2108,10 +2120,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121238149</v>
+        <v>121246773</v>
       </c>
       <c r="B12" t="n">
-        <v>78608</v>
+        <v>79690</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2124,21 +2136,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2147,14 +2159,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473540</v>
+        <v>473688</v>
       </c>
       <c r="R12" t="n">
-        <v>7046097</v>
+        <v>7046072</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2191,7 +2203,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Enstaka stora bålar av lunglav några meter upp på en grovbarkad sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2216,22 +2228,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2249,10 +2261,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121241286</v>
+        <v>121242466</v>
       </c>
       <c r="B13" t="n">
-        <v>79725</v>
+        <v>90738</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2261,32 +2273,40 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2296,10 +2316,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473521</v>
+        <v>473518</v>
       </c>
       <c r="R13" t="n">
-        <v>7046016</v>
+        <v>7045959</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2334,6 +2354,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2351,32 +2376,32 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>En grov sälglåga.</t>
+          <t>En smal död gran som är knäckt vid basen.</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2394,10 +2419,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121238339</v>
+        <v>121238082</v>
       </c>
       <c r="B14" t="n">
-        <v>91402</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2406,31 +2431,40 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
@@ -2475,13 +2509,17 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2507,12 +2545,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2530,10 +2568,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121241817</v>
+        <v>121231824</v>
       </c>
       <c r="B15" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2573,10 +2611,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473522</v>
+        <v>473642</v>
       </c>
       <c r="R15" t="n">
-        <v>7045984</v>
+        <v>7046059</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2613,7 +2651,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2633,7 +2671,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2671,10 +2709,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121245981</v>
+        <v>121240324</v>
       </c>
       <c r="B16" t="n">
-        <v>90737</v>
+        <v>79726</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2683,32 +2721,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2718,13 +2756,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473515</v>
+        <v>473527</v>
       </c>
       <c r="R16" t="n">
-        <v>7045852</v>
+        <v>7046057</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2754,11 +2792,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2778,27 +2811,32 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, båhål (hackspettar) i grov asp, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2816,10 +2854,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121238387</v>
+        <v>121247541</v>
       </c>
       <c r="B17" t="n">
-        <v>79718</v>
+        <v>79726</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2832,21 +2870,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2859,14 +2897,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473540</v>
+        <v>473680</v>
       </c>
       <c r="R17" t="n">
-        <v>7046097</v>
+        <v>7046060</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2931,14 +2969,19 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
+        </is>
+      </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2956,10 +2999,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121241235</v>
+        <v>121245981</v>
       </c>
       <c r="B18" t="n">
-        <v>79689</v>
+        <v>90738</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2972,28 +3015,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3003,13 +3046,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473521</v>
+        <v>473515</v>
       </c>
       <c r="R18" t="n">
-        <v>7046016</v>
+        <v>7045852</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3043,7 +3086,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3063,32 +3106,27 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, båhål (hackspettar) i grov asp, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3106,10 +3144,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121247541</v>
+        <v>121241304</v>
       </c>
       <c r="B19" t="n">
-        <v>79725</v>
+        <v>79719</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3122,21 +3160,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3153,10 +3191,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473680</v>
+        <v>473521</v>
       </c>
       <c r="R19" t="n">
-        <v>7046060</v>
+        <v>7046016</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3251,10 +3289,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121242466</v>
+        <v>121244830</v>
       </c>
       <c r="B20" t="n">
-        <v>90737</v>
+        <v>78609</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3267,38 +3305,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3306,10 +3332,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473518</v>
+        <v>473247</v>
       </c>
       <c r="R20" t="n">
-        <v>7045959</v>
+        <v>7045894</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3346,7 +3372,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3366,7 +3392,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3381,17 +3407,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>En smal död gran som är knäckt vid basen.</t>
+          <t>Flera granar.</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3409,7 +3435,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121246432</v>
+        <v>121247565</v>
       </c>
       <c r="B21" t="n">
         <v>79690</v>
@@ -3425,21 +3451,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3456,10 +3482,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473702</v>
+        <v>473680</v>
       </c>
       <c r="R21" t="n">
-        <v>7046035</v>
+        <v>7046060</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3496,7 +3522,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Enstaka bålar av lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3531,17 +3557,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>En flerstammig sälg.</t>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3559,10 +3585,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121238082</v>
+        <v>121241817</v>
       </c>
       <c r="B22" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3575,46 +3601,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473540</v>
+        <v>473522</v>
       </c>
       <c r="R22" t="n">
-        <v>7046097</v>
+        <v>7045984</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3651,7 +3668,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3660,6 +3677,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3670,7 +3688,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -3685,12 +3703,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3708,10 +3726,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121231830</v>
+        <v>121246631</v>
       </c>
       <c r="B23" t="n">
-        <v>78608</v>
+        <v>79719</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3720,30 +3738,34 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3751,10 +3773,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473557</v>
+        <v>473702</v>
       </c>
       <c r="R23" t="n">
-        <v>7046096</v>
+        <v>7046035</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3789,11 +3811,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3816,22 +3833,27 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3849,10 +3871,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121231824</v>
+        <v>121246432</v>
       </c>
       <c r="B24" t="n">
-        <v>78608</v>
+        <v>79691</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3865,26 +3887,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3892,10 +3918,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473642</v>
+        <v>473702</v>
       </c>
       <c r="R24" t="n">
-        <v>7046059</v>
+        <v>7046035</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3932,7 +3958,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3957,22 +3983,27 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3990,10 +4021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121244747</v>
+        <v>121231830</v>
       </c>
       <c r="B25" t="n">
-        <v>56559</v>
+        <v>78609</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -4006,53 +4037,40 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473482</v>
+        <v>473557</v>
       </c>
       <c r="R25" t="n">
-        <v>7045969</v>
+        <v>7046096</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -4086,7 +4104,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4095,6 +4113,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -4105,7 +4124,27 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4123,10 +4162,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121245697</v>
+        <v>121244747</v>
       </c>
       <c r="B26" t="n">
-        <v>78608</v>
+        <v>56560</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4139,40 +4178,53 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473293</v>
+        <v>473482</v>
       </c>
       <c r="R26" t="n">
-        <v>7045728</v>
+        <v>7045969</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4206,7 +4258,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4215,7 +4267,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -4226,27 +4277,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4264,10 +4295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121240324</v>
+        <v>121245877</v>
       </c>
       <c r="B27" t="n">
-        <v>79725</v>
+        <v>57372</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4276,45 +4307,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473527</v>
+        <v>473507</v>
       </c>
       <c r="R27" t="n">
-        <v>7046057</v>
+        <v>7045849</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4349,13 +4385,17 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4366,32 +4406,27 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4409,10 +4444,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121246207</v>
+        <v>121238339</v>
       </c>
       <c r="B28" t="n">
-        <v>90737</v>
+        <v>91403</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4421,52 +4456,44 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473595</v>
+        <v>473540</v>
       </c>
       <c r="R28" t="n">
-        <v>7046005</v>
+        <v>7046097</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4496,11 +4523,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Minst 8 st fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4520,7 +4542,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4535,12 +4557,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # En upplyft lutande stam av en knäckt gran. # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4558,10 +4580,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121241304</v>
+        <v>121244154</v>
       </c>
       <c r="B29" t="n">
-        <v>79718</v>
+        <v>78609</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4570,34 +4592,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4605,10 +4623,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473521</v>
+        <v>473456</v>
       </c>
       <c r="R29" t="n">
-        <v>7046016</v>
+        <v>7045981</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4643,6 +4661,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4660,32 +4683,27 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4703,10 +4721,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121244830</v>
+        <v>121231827</v>
       </c>
       <c r="B30" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4746,10 +4764,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473247</v>
+        <v>473583</v>
       </c>
       <c r="R30" t="n">
-        <v>7045894</v>
+        <v>7046084</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4786,7 +4804,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4806,7 +4824,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4819,11 +4837,6 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
       <c r="AM30" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -4831,7 +4844,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4849,7 +4862,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121247570</v>
+        <v>121238543</v>
       </c>
       <c r="B31" t="n">
         <v>79690</v>
@@ -4865,28 +4878,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4896,10 +4909,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473680</v>
+        <v>473527</v>
       </c>
       <c r="R31" t="n">
-        <v>7046060</v>
+        <v>7046057</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4936,7 +4949,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Enstaka bålar av skrovellav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Fina exemplar av lunglav på en gammal sälg där vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4971,17 +4984,17 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>En grov sälglåga.</t>
+          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4999,10 +5012,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121245877</v>
+        <v>121241235</v>
       </c>
       <c r="B32" t="n">
-        <v>57371</v>
+        <v>79690</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5015,46 +5028,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473507</v>
+        <v>473521</v>
       </c>
       <c r="R32" t="n">
-        <v>7045849</v>
+        <v>7046016</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -5091,7 +5099,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5100,6 +5108,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -5110,27 +5119,32 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5148,10 +5162,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121241506</v>
+        <v>121238149</v>
       </c>
       <c r="B33" t="n">
-        <v>78344</v>
+        <v>78609</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5164,21 +5178,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -5187,14 +5201,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473522</v>
+        <v>473540</v>
       </c>
       <c r="R33" t="n">
-        <v>7045984</v>
+        <v>7046097</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5231,7 +5245,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gott om kolflarnlav på en kolad tallhögstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5251,32 +5265,27 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>En ca 4 meter hög högstubbe.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris # En ca 4 meter hög högstubbe.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5294,10 +5303,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121247565</v>
+        <v>121245697</v>
       </c>
       <c r="B34" t="n">
-        <v>79689</v>
+        <v>78609</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5310,30 +5319,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -5341,10 +5346,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473680</v>
+        <v>473293</v>
       </c>
       <c r="R34" t="n">
-        <v>7046060</v>
+        <v>7045728</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5381,7 +5386,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5401,32 +5406,27 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5444,10 +5444,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121246773</v>
+        <v>121246191</v>
       </c>
       <c r="B35" t="n">
-        <v>79689</v>
+        <v>78345</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5460,21 +5460,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5487,13 +5487,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473688</v>
+        <v>473595</v>
       </c>
       <c r="R35" t="n">
-        <v>7046072</v>
+        <v>7046005</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Enstaka stora bålar av lunglav några meter upp på en grovbarkad sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5547,27 +5547,27 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121218973</v>
+        <v>121260476</v>
       </c>
       <c r="B36" t="n">
-        <v>90719</v>
+        <v>74707</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5601,21 +5601,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5628,13 +5628,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473506</v>
+        <v>473489</v>
       </c>
       <c r="R36" t="n">
-        <v>7046084</v>
+        <v>7046095</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5693,22 +5693,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Wood surface of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5726,10 +5726,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121260476</v>
+        <v>121218973</v>
       </c>
       <c r="B37" t="n">
-        <v>74706</v>
+        <v>90720</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5742,21 +5742,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5769,13 +5769,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473489</v>
+        <v>473506</v>
       </c>
       <c r="R37" t="n">
-        <v>7046095</v>
+        <v>7046084</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5834,22 +5834,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Betula</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>

--- a/artfynd/A 39937-2024 artfynd.xlsx
+++ b/artfynd/A 39937-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121219485</v>
+        <v>121219221</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -713,20 +713,24 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473631</v>
+        <v>473234</v>
       </c>
       <c r="R2" t="n">
-        <v>7045992</v>
+        <v>7045879</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -763,7 +767,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om färska ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1096,7 +1100,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121219221</v>
+        <v>121219485</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1134,24 +1138,20 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473234</v>
+        <v>473631</v>
       </c>
       <c r="R5" t="n">
-        <v>7045879</v>
+        <v>7045992</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Äldre ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121241286</v>
+        <v>121238082</v>
       </c>
       <c r="B6" t="n">
-        <v>79726</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1257,45 +1257,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473521</v>
+        <v>473540</v>
       </c>
       <c r="R6" t="n">
-        <v>7046016</v>
+        <v>7046097</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1330,13 +1335,17 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1352,27 +1361,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1390,10 +1394,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121241506</v>
+        <v>121244154</v>
       </c>
       <c r="B7" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1406,21 +1410,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1433,10 +1437,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473522</v>
+        <v>473456</v>
       </c>
       <c r="R7" t="n">
-        <v>7045984</v>
+        <v>7045981</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1473,7 +1477,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gott om kolflarnlav på en kolad tallhögstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1493,32 +1497,27 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>En ca 4 meter hög högstubbe.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris # En ca 4 meter hög högstubbe.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1536,10 +1535,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121246722</v>
+        <v>121245981</v>
       </c>
       <c r="B8" t="n">
-        <v>79725</v>
+        <v>90738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1548,32 +1547,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1583,13 +1582,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473702</v>
+        <v>473515</v>
       </c>
       <c r="R8" t="n">
-        <v>7046035</v>
+        <v>7045852</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1619,6 +1618,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1638,32 +1642,27 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, båhål (hackspettar) i grov asp, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>En flerstammig sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1681,10 +1680,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121246207</v>
+        <v>121246631</v>
       </c>
       <c r="B9" t="n">
-        <v>90738</v>
+        <v>79719</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1693,38 +1692,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1732,13 +1727,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473595</v>
+        <v>473702</v>
       </c>
       <c r="R9" t="n">
-        <v>7046005</v>
+        <v>7046035</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1768,11 +1763,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 8 st fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1792,27 +1782,32 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # En upplyft lutande stam av en knäckt gran. # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1830,10 +1825,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121247570</v>
+        <v>121242466</v>
       </c>
       <c r="B10" t="n">
-        <v>79691</v>
+        <v>90738</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1846,28 +1841,36 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1877,10 +1880,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473680</v>
+        <v>473518</v>
       </c>
       <c r="R10" t="n">
-        <v>7046060</v>
+        <v>7045959</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1917,7 +1920,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Enstaka bålar av skrovellav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1937,32 +1940,32 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>En grov sälglåga.</t>
+          <t>En smal död gran som är knäckt vid basen.</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2120,7 +2123,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121246773</v>
+        <v>121238543</v>
       </c>
       <c r="B12" t="n">
         <v>79690</v>
@@ -2155,7 +2158,11 @@
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2163,10 +2170,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473688</v>
+        <v>473527</v>
       </c>
       <c r="R12" t="n">
-        <v>7046072</v>
+        <v>7046057</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2203,7 +2210,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Enstaka stora bålar av lunglav några meter upp på en grovbarkad sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Fina exemplar av lunglav på en gammal sälg där vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2236,6 +2243,11 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+        </is>
+      </c>
       <c r="AM12" t="inlineStr">
         <is>
           <t>Bark på levande träd</t>
@@ -2243,7 +2255,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2261,10 +2273,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121242466</v>
+        <v>121238149</v>
       </c>
       <c r="B13" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2277,49 +2289,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473518</v>
+        <v>473540</v>
       </c>
       <c r="R13" t="n">
-        <v>7045959</v>
+        <v>7046097</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2389,19 +2389,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>En smal död gran som är knäckt vid basen.</t>
-        </is>
-      </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2419,10 +2414,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121238082</v>
+        <v>121241817</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2435,46 +2430,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473540</v>
+        <v>473522</v>
       </c>
       <c r="R14" t="n">
-        <v>7046097</v>
+        <v>7045984</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2511,7 +2497,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2520,6 +2506,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2530,7 +2517,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2545,12 +2532,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2568,10 +2555,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121231824</v>
+        <v>121246722</v>
       </c>
       <c r="B15" t="n">
-        <v>78609</v>
+        <v>79725</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2580,20 +2567,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2603,7 +2590,11 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2611,10 +2602,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473642</v>
+        <v>473702</v>
       </c>
       <c r="R15" t="n">
-        <v>7046059</v>
+        <v>7046035</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2649,11 +2640,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2676,22 +2662,27 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2709,10 +2700,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121240324</v>
+        <v>121247570</v>
       </c>
       <c r="B16" t="n">
-        <v>79726</v>
+        <v>79691</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2721,32 +2712,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2756,10 +2747,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473527</v>
+        <v>473680</v>
       </c>
       <c r="R16" t="n">
-        <v>7046057</v>
+        <v>7046060</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2794,6 +2785,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Enstaka bålar av skrovellav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2826,17 +2822,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2854,10 +2850,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121247541</v>
+        <v>121246207</v>
       </c>
       <c r="B17" t="n">
-        <v>79726</v>
+        <v>90738</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2866,34 +2862,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2901,13 +2901,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473680</v>
+        <v>473595</v>
       </c>
       <c r="R17" t="n">
-        <v>7046060</v>
+        <v>7046005</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2937,6 +2937,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 8 st fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2956,32 +2961,27 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Horizontal, dead without ground contact # En upplyft lutande stam av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2999,10 +2999,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121245981</v>
+        <v>121241304</v>
       </c>
       <c r="B18" t="n">
-        <v>90738</v>
+        <v>79719</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3011,32 +3011,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3046,13 +3046,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473515</v>
+        <v>473521</v>
       </c>
       <c r="R18" t="n">
-        <v>7045852</v>
+        <v>7046016</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3082,11 +3082,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3106,27 +3101,32 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, båhål (hackspettar) i grov asp, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3144,10 +3144,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121241304</v>
+        <v>121231827</v>
       </c>
       <c r="B19" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3156,34 +3156,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3191,10 +3187,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473521</v>
+        <v>473583</v>
       </c>
       <c r="R19" t="n">
-        <v>7046016</v>
+        <v>7046084</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3229,6 +3225,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3251,27 +3252,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3289,10 +3285,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121244830</v>
+        <v>121246432</v>
       </c>
       <c r="B20" t="n">
-        <v>78609</v>
+        <v>79691</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3305,26 +3301,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473247</v>
+        <v>473702</v>
       </c>
       <c r="R20" t="n">
-        <v>7045894</v>
+        <v>7046035</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3392,32 +3392,32 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Flera granar.</t>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3435,10 +3435,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121247565</v>
+        <v>121246191</v>
       </c>
       <c r="B21" t="n">
-        <v>79690</v>
+        <v>78345</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3451,30 +3451,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3482,13 +3478,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473680</v>
+        <v>473595</v>
       </c>
       <c r="R21" t="n">
-        <v>7046060</v>
+        <v>7046005</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3522,7 +3518,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3542,32 +3538,27 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3585,10 +3576,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121241817</v>
+        <v>121241506</v>
       </c>
       <c r="B22" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3601,21 +3592,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3668,7 +3659,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om kolflarnlav på en kolad tallhögstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3693,22 +3684,27 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>En ca 4 meter hög högstubbe.</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris # En ca 4 meter hög högstubbe.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3726,10 +3722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121246631</v>
+        <v>121241286</v>
       </c>
       <c r="B23" t="n">
-        <v>79719</v>
+        <v>79726</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3742,21 +3738,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3773,10 +3769,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473702</v>
+        <v>473521</v>
       </c>
       <c r="R23" t="n">
-        <v>7046035</v>
+        <v>7046016</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3843,17 +3839,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>En flerstammig sälg.</t>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3871,10 +3867,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121246432</v>
+        <v>121241235</v>
       </c>
       <c r="B24" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3887,21 +3883,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3918,10 +3914,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473702</v>
+        <v>473521</v>
       </c>
       <c r="R24" t="n">
-        <v>7046035</v>
+        <v>7046016</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3958,7 +3954,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3993,17 +3989,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>En flerstammig sälg.</t>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -4021,10 +4017,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121231830</v>
+        <v>121247541</v>
       </c>
       <c r="B25" t="n">
-        <v>78609</v>
+        <v>79726</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -4033,30 +4029,34 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473557</v>
+        <v>473680</v>
       </c>
       <c r="R25" t="n">
-        <v>7046096</v>
+        <v>7046060</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -4102,11 +4102,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -4129,22 +4124,27 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4162,10 +4162,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121244747</v>
+        <v>121246773</v>
       </c>
       <c r="B26" t="n">
-        <v>56560</v>
+        <v>79690</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4178,53 +4178,40 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473482</v>
+        <v>473688</v>
       </c>
       <c r="R26" t="n">
-        <v>7045969</v>
+        <v>7046072</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4258,7 +4245,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Enstaka stora bålar av lunglav några meter upp på en grovbarkad sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4267,6 +4254,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -4277,7 +4265,27 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4295,10 +4303,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121245877</v>
+        <v>121238339</v>
       </c>
       <c r="B27" t="n">
-        <v>57372</v>
+        <v>91403</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4307,50 +4315,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473507</v>
+        <v>473540</v>
       </c>
       <c r="R27" t="n">
-        <v>7045849</v>
+        <v>7046097</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4385,17 +4384,13 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4406,7 +4401,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -4421,12 +4416,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4444,10 +4439,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121238339</v>
+        <v>121231830</v>
       </c>
       <c r="B28" t="n">
-        <v>91403</v>
+        <v>78609</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4456,25 +4451,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4483,14 +4478,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473540</v>
+        <v>473557</v>
       </c>
       <c r="R28" t="n">
-        <v>7046097</v>
+        <v>7046096</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4525,6 +4520,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4557,12 +4557,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4580,7 +4580,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121244154</v>
+        <v>121231824</v>
       </c>
       <c r="B29" t="n">
         <v>78609</v>
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473456</v>
+        <v>473642</v>
       </c>
       <c r="R29" t="n">
-        <v>7045981</v>
+        <v>7046059</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4721,10 +4721,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121231827</v>
+        <v>121240324</v>
       </c>
       <c r="B30" t="n">
-        <v>78609</v>
+        <v>79726</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4733,30 +4733,34 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4764,10 +4768,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473583</v>
+        <v>473527</v>
       </c>
       <c r="R30" t="n">
-        <v>7046084</v>
+        <v>7046057</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4802,11 +4806,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4829,22 +4828,27 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4862,10 +4866,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121238543</v>
+        <v>121245697</v>
       </c>
       <c r="B31" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4878,30 +4882,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473527</v>
+        <v>473293</v>
       </c>
       <c r="R31" t="n">
-        <v>7046057</v>
+        <v>7045728</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Fina exemplar av lunglav på en gammal sälg där vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4969,32 +4969,27 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -5012,10 +5007,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121241235</v>
+        <v>121244747</v>
       </c>
       <c r="B32" t="n">
-        <v>79690</v>
+        <v>56560</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5028,44 +5023,53 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473521</v>
+        <v>473482</v>
       </c>
       <c r="R32" t="n">
-        <v>7046016</v>
+        <v>7045969</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -5099,7 +5103,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5108,7 +5112,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -5119,32 +5122,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5162,7 +5140,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121238149</v>
+        <v>121244830</v>
       </c>
       <c r="B33" t="n">
         <v>78609</v>
@@ -5201,14 +5179,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473540</v>
+        <v>473247</v>
       </c>
       <c r="R33" t="n">
-        <v>7046097</v>
+        <v>7045894</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5265,7 +5243,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -5278,6 +5256,11 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
       <c r="AM33" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -5285,7 +5268,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5303,10 +5286,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121245697</v>
+        <v>121245877</v>
       </c>
       <c r="B34" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5319,37 +5302,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473293</v>
+        <v>473507</v>
       </c>
       <c r="R34" t="n">
-        <v>7045728</v>
+        <v>7045849</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5386,7 +5378,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5395,7 +5387,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5406,7 +5397,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -5421,12 +5412,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5444,10 +5435,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121246191</v>
+        <v>121247565</v>
       </c>
       <c r="B35" t="n">
-        <v>78345</v>
+        <v>79690</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5460,26 +5451,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5487,13 +5482,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473595</v>
+        <v>473680</v>
       </c>
       <c r="R35" t="n">
-        <v>7046005</v>
+        <v>7046060</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5527,7 +5522,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Enstaka bålar av lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5547,27 +5542,32 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121260476</v>
+        <v>121218973</v>
       </c>
       <c r="B36" t="n">
-        <v>74707</v>
+        <v>90720</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5601,21 +5601,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5628,13 +5628,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473489</v>
+        <v>473506</v>
       </c>
       <c r="R36" t="n">
-        <v>7046095</v>
+        <v>7046084</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5693,22 +5693,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Betula</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5726,10 +5726,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121218973</v>
+        <v>121260476</v>
       </c>
       <c r="B37" t="n">
-        <v>90720</v>
+        <v>74707</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5742,21 +5742,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5769,13 +5769,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473506</v>
+        <v>473489</v>
       </c>
       <c r="R37" t="n">
-        <v>7046084</v>
+        <v>7046095</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5834,22 +5834,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Wood surface of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>

--- a/artfynd/A 39937-2024 artfynd.xlsx
+++ b/artfynd/A 39937-2024 artfynd.xlsx
@@ -824,7 +824,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121219127</v>
+        <v>121219351</v>
       </c>
       <c r="B3" t="n">
         <v>98105</v>
@@ -859,7 +859,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -884,10 +884,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473560</v>
+        <v>473214</v>
       </c>
       <c r="R3" t="n">
-        <v>7046115</v>
+        <v>7045971</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -924,7 +924,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Knärot med minst 33 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -962,10 +962,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121219351</v>
+        <v>121219485</v>
       </c>
       <c r="B4" t="n">
-        <v>98105</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -974,58 +974,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473214</v>
+        <v>473631</v>
       </c>
       <c r="R4" t="n">
-        <v>7045971</v>
+        <v>7045992</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1062,7 +1050,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Äldre ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1071,7 +1059,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1083,6 +1070,26 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1100,10 +1107,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121219485</v>
+        <v>121219127</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1112,46 +1119,58 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473631</v>
+        <v>473560</v>
       </c>
       <c r="R5" t="n">
-        <v>7045992</v>
+        <v>7046115</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1188,7 +1207,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Knärot med minst 33 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1197,6 +1216,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1208,26 +1228,6 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121238082</v>
+        <v>121238387</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>79719</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1257,40 +1257,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
@@ -1335,17 +1330,13 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1361,22 +1352,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1394,7 +1385,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121244154</v>
+        <v>121244830</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1437,10 +1428,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473456</v>
+        <v>473247</v>
       </c>
       <c r="R7" t="n">
-        <v>7045981</v>
+        <v>7045894</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1497,7 +1488,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1510,6 +1501,11 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
       <c r="AM7" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -1517,7 +1513,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1535,7 +1531,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121245981</v>
+        <v>121242466</v>
       </c>
       <c r="B8" t="n">
         <v>90738</v>
@@ -1568,8 +1564,16 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -1582,13 +1586,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473515</v>
+        <v>473518</v>
       </c>
       <c r="R8" t="n">
-        <v>7045852</v>
+        <v>7045959</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1642,7 +1646,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, båhål (hackspettar) i grov asp, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1655,6 +1659,11 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>En smal död gran som är knäckt vid basen.</t>
+        </is>
+      </c>
       <c r="AM8" t="inlineStr">
         <is>
           <t>Liggande död trädstam, utan markontakt</t>
@@ -1662,7 +1671,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1680,10 +1689,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121246631</v>
+        <v>121231824</v>
       </c>
       <c r="B9" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1692,34 +1701,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1727,10 +1732,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473702</v>
+        <v>473642</v>
       </c>
       <c r="R9" t="n">
-        <v>7046035</v>
+        <v>7046059</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1765,6 +1770,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1787,27 +1797,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>En flerstammig sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1825,10 +1830,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121242466</v>
+        <v>121246722</v>
       </c>
       <c r="B10" t="n">
-        <v>90738</v>
+        <v>79725</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1837,40 +1842,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1880,10 +1877,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473518</v>
+        <v>473702</v>
       </c>
       <c r="R10" t="n">
-        <v>7045959</v>
+        <v>7046035</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1918,11 +1915,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1940,32 +1932,32 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>En smal död gran som är knäckt vid basen.</t>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1983,10 +1975,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121238387</v>
+        <v>121246432</v>
       </c>
       <c r="B11" t="n">
-        <v>79719</v>
+        <v>79691</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1995,45 +1987,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473540</v>
+        <v>473702</v>
       </c>
       <c r="R11" t="n">
-        <v>7046097</v>
+        <v>7046035</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2068,6 +2060,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -2098,6 +2095,11 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>En flerstammig sälg.</t>
+        </is>
+      </c>
       <c r="AM11" t="inlineStr">
         <is>
           <t>Bark på levande träd</t>
@@ -2105,7 +2107,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2123,10 +2125,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121238543</v>
+        <v>121241304</v>
       </c>
       <c r="B12" t="n">
-        <v>79690</v>
+        <v>79719</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2135,25 +2137,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2170,10 +2172,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473527</v>
+        <v>473521</v>
       </c>
       <c r="R12" t="n">
-        <v>7046057</v>
+        <v>7046016</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2208,11 +2210,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Fina exemplar av lunglav på en gammal sälg där vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2245,17 +2242,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2273,10 +2270,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121238149</v>
+        <v>121246773</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2289,21 +2286,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2312,14 +2309,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473540</v>
+        <v>473688</v>
       </c>
       <c r="R13" t="n">
-        <v>7046097</v>
+        <v>7046072</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2356,7 +2353,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Enstaka stora bålar av lunglav några meter upp på en grovbarkad sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2381,22 +2378,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2414,7 +2411,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121241817</v>
+        <v>121244154</v>
       </c>
       <c r="B14" t="n">
         <v>78609</v>
@@ -2457,10 +2454,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473522</v>
+        <v>473456</v>
       </c>
       <c r="R14" t="n">
-        <v>7045984</v>
+        <v>7045981</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2517,7 +2514,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2555,10 +2552,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121246722</v>
+        <v>121244747</v>
       </c>
       <c r="B15" t="n">
-        <v>79725</v>
+        <v>56560</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2567,48 +2564,57 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473702</v>
+        <v>473482</v>
       </c>
       <c r="R15" t="n">
-        <v>7046035</v>
+        <v>7045969</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2640,13 +2646,17 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2657,32 +2667,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>En flerstammig sälg.</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2700,10 +2685,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121247570</v>
+        <v>121247541</v>
       </c>
       <c r="B16" t="n">
-        <v>79691</v>
+        <v>79726</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2712,32 +2697,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2783,11 +2768,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Enstaka bålar av skrovellav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2850,10 +2830,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121246207</v>
+        <v>121240324</v>
       </c>
       <c r="B17" t="n">
-        <v>90738</v>
+        <v>79726</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2862,38 +2842,34 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2901,13 +2877,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473595</v>
+        <v>473527</v>
       </c>
       <c r="R17" t="n">
-        <v>7046005</v>
+        <v>7046057</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2937,11 +2913,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Minst 8 st fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2961,27 +2932,32 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # En upplyft lutande stam av en knäckt gran. # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2999,10 +2975,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121241304</v>
+        <v>121231830</v>
       </c>
       <c r="B18" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3011,34 +2987,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -3046,10 +3018,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473521</v>
+        <v>473557</v>
       </c>
       <c r="R18" t="n">
-        <v>7046016</v>
+        <v>7046096</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3084,6 +3056,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -3106,27 +3083,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3285,10 +3257,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121246432</v>
+        <v>121238543</v>
       </c>
       <c r="B20" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3301,28 +3273,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3332,10 +3304,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473702</v>
+        <v>473527</v>
       </c>
       <c r="R20" t="n">
-        <v>7046035</v>
+        <v>7046057</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3372,7 +3344,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Fina exemplar av lunglav på en gammal sälg där vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3407,7 +3379,7 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>En flerstammig sälg.</t>
+          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -3417,7 +3389,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3435,10 +3407,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121246191</v>
+        <v>121247565</v>
       </c>
       <c r="B21" t="n">
-        <v>78345</v>
+        <v>79690</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3451,26 +3423,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3478,13 +3454,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473595</v>
+        <v>473680</v>
       </c>
       <c r="R21" t="n">
-        <v>7046005</v>
+        <v>7046060</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3518,7 +3494,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Enstaka bålar av lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3538,27 +3514,32 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3576,10 +3557,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121241506</v>
+        <v>121247570</v>
       </c>
       <c r="B22" t="n">
-        <v>78345</v>
+        <v>79691</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3592,26 +3573,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3619,10 +3604,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473522</v>
+        <v>473680</v>
       </c>
       <c r="R22" t="n">
-        <v>7045984</v>
+        <v>7046060</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3659,7 +3644,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Gott om kolflarnlav på en kolad tallhögstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Enstaka bålar av skrovellav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3679,32 +3664,32 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>En ca 4 meter hög högstubbe.</t>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris # En ca 4 meter hög högstubbe.</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3722,10 +3707,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121241286</v>
+        <v>121238339</v>
       </c>
       <c r="B23" t="n">
-        <v>79726</v>
+        <v>91403</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3738,41 +3723,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473521</v>
+        <v>473540</v>
       </c>
       <c r="R23" t="n">
-        <v>7046016</v>
+        <v>7046097</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3829,27 +3810,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3867,10 +3843,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121241235</v>
+        <v>121238082</v>
       </c>
       <c r="B24" t="n">
-        <v>79690</v>
+        <v>57356</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3883,41 +3859,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473521</v>
+        <v>473540</v>
       </c>
       <c r="R24" t="n">
-        <v>7046016</v>
+        <v>7046097</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3954,7 +3935,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3963,7 +3944,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3979,27 +3959,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -4017,10 +3992,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121247541</v>
+        <v>121246207</v>
       </c>
       <c r="B25" t="n">
-        <v>79726</v>
+        <v>90738</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -4029,34 +4004,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -4064,13 +4043,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473680</v>
+        <v>473595</v>
       </c>
       <c r="R25" t="n">
-        <v>7046060</v>
+        <v>7046005</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -4100,6 +4079,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Minst 8 st fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4119,32 +4103,27 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Horizontal, dead without ground contact # En upplyft lutande stam av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4162,7 +4141,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121246773</v>
+        <v>121241235</v>
       </c>
       <c r="B26" t="n">
         <v>79690</v>
@@ -4197,7 +4176,11 @@
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -4205,10 +4188,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473688</v>
+        <v>473521</v>
       </c>
       <c r="R26" t="n">
-        <v>7046072</v>
+        <v>7046016</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4245,7 +4228,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Enstaka stora bålar av lunglav några meter upp på en grovbarkad sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4278,14 +4261,19 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
+        </is>
+      </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4303,10 +4291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121238339</v>
+        <v>121241817</v>
       </c>
       <c r="B27" t="n">
-        <v>91403</v>
+        <v>78609</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4315,25 +4303,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -4342,14 +4330,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473540</v>
+        <v>473522</v>
       </c>
       <c r="R27" t="n">
-        <v>7046097</v>
+        <v>7045984</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4384,6 +4372,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4401,7 +4394,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -4416,12 +4409,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4439,10 +4432,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121231830</v>
+        <v>121241286</v>
       </c>
       <c r="B28" t="n">
-        <v>78609</v>
+        <v>79726</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4451,30 +4444,34 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4482,10 +4479,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473557</v>
+        <v>473521</v>
       </c>
       <c r="R28" t="n">
-        <v>7046096</v>
+        <v>7046016</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4520,11 +4517,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4547,22 +4539,27 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4580,10 +4577,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121231824</v>
+        <v>121245877</v>
       </c>
       <c r="B29" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4596,37 +4593,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473642</v>
+        <v>473507</v>
       </c>
       <c r="R29" t="n">
-        <v>7046059</v>
+        <v>7045849</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4663,7 +4669,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4672,7 +4678,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4683,7 +4688,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4698,12 +4703,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4721,10 +4726,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121240324</v>
+        <v>121246631</v>
       </c>
       <c r="B30" t="n">
-        <v>79726</v>
+        <v>79719</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4737,21 +4742,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4768,10 +4773,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473527</v>
+        <v>473702</v>
       </c>
       <c r="R30" t="n">
-        <v>7046057</v>
+        <v>7046035</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4838,7 +4843,7 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4848,7 +4853,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -5007,10 +5012,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121244747</v>
+        <v>121246191</v>
       </c>
       <c r="B32" t="n">
-        <v>56560</v>
+        <v>78345</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5023,53 +5028,40 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473482</v>
+        <v>473595</v>
       </c>
       <c r="R32" t="n">
-        <v>7045969</v>
+        <v>7046005</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -5103,7 +5095,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5112,6 +5104,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -5122,7 +5115,27 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5140,10 +5153,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121244830</v>
+        <v>121241506</v>
       </c>
       <c r="B33" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5156,21 +5169,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -5183,10 +5196,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473247</v>
+        <v>473522</v>
       </c>
       <c r="R33" t="n">
-        <v>7045894</v>
+        <v>7045984</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5223,7 +5236,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om kolflarnlav på en kolad tallhögstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5243,32 +5256,32 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>Flera granar.</t>
+          <t>En ca 4 meter hög högstubbe.</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris # En ca 4 meter hög högstubbe.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5286,10 +5299,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121245877</v>
+        <v>121245981</v>
       </c>
       <c r="B34" t="n">
-        <v>57372</v>
+        <v>90738</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5302,49 +5315,44 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473507</v>
+        <v>473515</v>
       </c>
       <c r="R34" t="n">
-        <v>7045849</v>
+        <v>7045852</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5378,7 +5386,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5387,6 +5395,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5397,7 +5406,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, båhål (hackspettar) i grov asp, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -5412,12 +5421,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5435,10 +5444,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121247565</v>
+        <v>121238149</v>
       </c>
       <c r="B35" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5451,41 +5460,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473680</v>
+        <v>473540</v>
       </c>
       <c r="R35" t="n">
-        <v>7046060</v>
+        <v>7046097</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5522,7 +5527,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5547,27 +5552,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>

--- a/artfynd/A 39937-2024 artfynd.xlsx
+++ b/artfynd/A 39937-2024 artfynd.xlsx
@@ -1245,10 +1245,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121238387</v>
+        <v>121247570</v>
       </c>
       <c r="B6" t="n">
-        <v>79719</v>
+        <v>79691</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1257,45 +1257,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473540</v>
+        <v>473680</v>
       </c>
       <c r="R6" t="n">
-        <v>7046097</v>
+        <v>7046060</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1330,6 +1330,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Enstaka bålar av skrovellav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1360,14 +1365,19 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
+        </is>
+      </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1385,7 +1395,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121244830</v>
+        <v>121238149</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1424,14 +1434,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473247</v>
+        <v>473540</v>
       </c>
       <c r="R7" t="n">
-        <v>7045894</v>
+        <v>7046097</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1488,7 +1498,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1501,11 +1511,6 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
       <c r="AM7" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -1513,7 +1518,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1531,10 +1536,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121242466</v>
+        <v>121231824</v>
       </c>
       <c r="B8" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1547,38 +1552,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1586,10 +1579,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473518</v>
+        <v>473642</v>
       </c>
       <c r="R8" t="n">
-        <v>7045959</v>
+        <v>7046059</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1626,7 +1619,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1646,7 +1639,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1659,19 +1652,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>En smal död gran som är knäckt vid basen.</t>
-        </is>
-      </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1689,7 +1677,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121231824</v>
+        <v>121244830</v>
       </c>
       <c r="B9" t="n">
         <v>78609</v>
@@ -1732,10 +1720,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473642</v>
+        <v>473247</v>
       </c>
       <c r="R9" t="n">
-        <v>7046059</v>
+        <v>7045894</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1772,7 +1760,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1792,7 +1780,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1805,6 +1793,11 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
       <c r="AM9" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -1812,7 +1805,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1830,10 +1823,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246722</v>
+        <v>121231827</v>
       </c>
       <c r="B10" t="n">
-        <v>79725</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1842,20 +1835,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1865,11 +1858,7 @@
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1877,10 +1866,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473702</v>
+        <v>473583</v>
       </c>
       <c r="R10" t="n">
-        <v>7046035</v>
+        <v>7046084</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1915,6 +1904,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1937,27 +1931,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>En flerstammig sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1975,10 +1964,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121246432</v>
+        <v>121241817</v>
       </c>
       <c r="B11" t="n">
-        <v>79691</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1991,30 +1980,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -2022,10 +2007,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473702</v>
+        <v>473522</v>
       </c>
       <c r="R11" t="n">
-        <v>7046035</v>
+        <v>7045984</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2062,7 +2047,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2082,32 +2067,27 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>En flerstammig sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2125,10 +2105,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121241304</v>
+        <v>121246773</v>
       </c>
       <c r="B12" t="n">
-        <v>79719</v>
+        <v>79690</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2137,34 +2117,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2172,10 +2148,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473521</v>
+        <v>473688</v>
       </c>
       <c r="R12" t="n">
-        <v>7046016</v>
+        <v>7046072</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2210,6 +2186,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Enstaka stora bålar av lunglav några meter upp på en grovbarkad sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2240,19 +2221,14 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
-        </is>
-      </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2270,10 +2246,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121246773</v>
+        <v>121238339</v>
       </c>
       <c r="B13" t="n">
-        <v>79690</v>
+        <v>91403</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2282,25 +2258,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2309,14 +2285,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473688</v>
+        <v>473540</v>
       </c>
       <c r="R13" t="n">
-        <v>7046072</v>
+        <v>7046097</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2351,11 +2327,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Enstaka stora bålar av lunglav några meter upp på en grovbarkad sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2378,22 +2349,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2411,7 +2382,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121244154</v>
+        <v>121231830</v>
       </c>
       <c r="B14" t="n">
         <v>78609</v>
@@ -2454,10 +2425,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473456</v>
+        <v>473557</v>
       </c>
       <c r="R14" t="n">
-        <v>7045981</v>
+        <v>7046096</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2494,7 +2465,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2514,7 +2485,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2552,10 +2523,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121244747</v>
+        <v>121246191</v>
       </c>
       <c r="B15" t="n">
-        <v>56560</v>
+        <v>78345</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2568,53 +2539,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473482</v>
+        <v>473595</v>
       </c>
       <c r="R15" t="n">
-        <v>7045969</v>
+        <v>7046005</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2648,7 +2606,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2657,6 +2615,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2667,7 +2626,27 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2685,10 +2664,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121247541</v>
+        <v>121244747</v>
       </c>
       <c r="B16" t="n">
-        <v>79726</v>
+        <v>56560</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2697,48 +2676,57 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473680</v>
+        <v>473482</v>
       </c>
       <c r="R16" t="n">
-        <v>7046060</v>
+        <v>7045969</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2770,13 +2758,17 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2787,32 +2779,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2975,10 +2942,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121231830</v>
+        <v>121242466</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2991,26 +2958,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -3018,10 +2997,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473557</v>
+        <v>473518</v>
       </c>
       <c r="R18" t="n">
-        <v>7046096</v>
+        <v>7045959</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3058,7 +3037,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3078,7 +3057,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3091,14 +3070,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>En smal död gran som är knäckt vid basen.</t>
+        </is>
+      </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3116,10 +3100,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121231827</v>
+        <v>121245981</v>
       </c>
       <c r="B19" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3132,26 +3116,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3159,13 +3147,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473583</v>
+        <v>473515</v>
       </c>
       <c r="R19" t="n">
-        <v>7046084</v>
+        <v>7045852</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3199,7 +3187,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3219,7 +3207,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, båhål (hackspettar) i grov asp, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3234,12 +3222,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3257,10 +3245,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121238543</v>
+        <v>121241506</v>
       </c>
       <c r="B20" t="n">
-        <v>79690</v>
+        <v>78345</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3273,30 +3261,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3304,10 +3288,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473527</v>
+        <v>473522</v>
       </c>
       <c r="R20" t="n">
-        <v>7046057</v>
+        <v>7045984</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3344,7 +3328,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Fina exemplar av lunglav på en gammal sälg där vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om kolflarnlav på en kolad tallhögstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3364,32 +3348,32 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>En ca 4 meter hög högstubbe.</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris # En ca 4 meter hög högstubbe.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3407,10 +3391,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121247565</v>
+        <v>121246207</v>
       </c>
       <c r="B21" t="n">
-        <v>79690</v>
+        <v>90738</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3423,30 +3407,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3454,13 +3442,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473680</v>
+        <v>473595</v>
       </c>
       <c r="R21" t="n">
-        <v>7046060</v>
+        <v>7046005</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3494,7 +3482,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Minst 8 st fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3514,32 +3502,27 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Horizontal, dead without ground contact # En upplyft lutande stam av en knäckt gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3557,10 +3540,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121247570</v>
+        <v>121245877</v>
       </c>
       <c r="B22" t="n">
-        <v>79691</v>
+        <v>57372</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3573,41 +3556,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473680</v>
+        <v>473507</v>
       </c>
       <c r="R22" t="n">
-        <v>7046060</v>
+        <v>7045849</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3644,7 +3632,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Enstaka bålar av skrovellav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3653,7 +3641,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3664,32 +3651,27 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3707,10 +3689,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121238339</v>
+        <v>121238387</v>
       </c>
       <c r="B23" t="n">
-        <v>91403</v>
+        <v>79719</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3723,26 +3705,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3810,22 +3796,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3843,10 +3829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121238082</v>
+        <v>121246631</v>
       </c>
       <c r="B24" t="n">
-        <v>57356</v>
+        <v>79719</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3855,50 +3841,45 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473540</v>
+        <v>473702</v>
       </c>
       <c r="R24" t="n">
-        <v>7046097</v>
+        <v>7046035</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3933,17 +3914,13 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3959,22 +3936,27 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3992,10 +3974,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121246207</v>
+        <v>121241286</v>
       </c>
       <c r="B25" t="n">
-        <v>90738</v>
+        <v>79726</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -4004,38 +3986,34 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -4043,13 +4021,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473595</v>
+        <v>473521</v>
       </c>
       <c r="R25" t="n">
-        <v>7046005</v>
+        <v>7046016</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -4079,11 +4057,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Minst 8 st fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4103,27 +4076,32 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # En upplyft lutande stam av en knäckt gran. # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4141,10 +4119,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121241235</v>
+        <v>121247541</v>
       </c>
       <c r="B26" t="n">
-        <v>79690</v>
+        <v>79726</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4153,32 +4131,32 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -4188,10 +4166,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473521</v>
+        <v>473680</v>
       </c>
       <c r="R26" t="n">
-        <v>7046016</v>
+        <v>7046060</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4224,11 +4202,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4291,10 +4264,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121241817</v>
+        <v>121246722</v>
       </c>
       <c r="B27" t="n">
-        <v>78609</v>
+        <v>79725</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4303,20 +4276,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4326,7 +4299,11 @@
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4334,10 +4311,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473522</v>
+        <v>473702</v>
       </c>
       <c r="R27" t="n">
-        <v>7045984</v>
+        <v>7046035</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4372,11 +4349,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4394,27 +4366,32 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4432,10 +4409,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121241286</v>
+        <v>121246432</v>
       </c>
       <c r="B28" t="n">
-        <v>79726</v>
+        <v>79691</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4444,32 +4421,32 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4479,10 +4456,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473521</v>
+        <v>473702</v>
       </c>
       <c r="R28" t="n">
-        <v>7046016</v>
+        <v>7046035</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4517,6 +4494,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4549,17 +4531,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>En grov sälglåga.</t>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4577,10 +4559,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121245877</v>
+        <v>121238543</v>
       </c>
       <c r="B29" t="n">
-        <v>57372</v>
+        <v>79690</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4593,46 +4575,41 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473507</v>
+        <v>473527</v>
       </c>
       <c r="R29" t="n">
-        <v>7045849</v>
+        <v>7046057</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4669,7 +4646,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Fina exemplar av lunglav på en gammal sälg där vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4678,6 +4655,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4688,27 +4666,32 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4726,10 +4709,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121246631</v>
+        <v>121244154</v>
       </c>
       <c r="B30" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4738,34 +4721,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4773,10 +4752,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473702</v>
+        <v>473456</v>
       </c>
       <c r="R30" t="n">
-        <v>7046035</v>
+        <v>7045981</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4811,6 +4790,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4828,32 +4812,27 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>En flerstammig sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4871,10 +4850,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121245697</v>
+        <v>121238082</v>
       </c>
       <c r="B31" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4887,37 +4866,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473293</v>
+        <v>473540</v>
       </c>
       <c r="R31" t="n">
-        <v>7045728</v>
+        <v>7046097</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4954,7 +4942,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4963,7 +4951,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4974,7 +4961,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4989,12 +4976,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -5012,10 +4999,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121246191</v>
+        <v>121241235</v>
       </c>
       <c r="B32" t="n">
-        <v>78345</v>
+        <v>79690</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5028,26 +5015,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -5055,13 +5046,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473595</v>
+        <v>473521</v>
       </c>
       <c r="R32" t="n">
-        <v>7046005</v>
+        <v>7046016</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -5095,7 +5086,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5115,27 +5106,32 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5153,10 +5149,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121241506</v>
+        <v>121241304</v>
       </c>
       <c r="B33" t="n">
-        <v>78345</v>
+        <v>79719</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5165,30 +5161,34 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -5196,10 +5196,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473522</v>
+        <v>473521</v>
       </c>
       <c r="R33" t="n">
-        <v>7045984</v>
+        <v>7046016</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5234,11 +5234,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Gott om kolflarnlav på en kolad tallhögstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -5256,32 +5251,32 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>En ca 4 meter hög högstubbe.</t>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris # En ca 4 meter hög högstubbe.</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5299,10 +5294,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121245981</v>
+        <v>121247565</v>
       </c>
       <c r="B34" t="n">
-        <v>90738</v>
+        <v>79690</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5315,28 +5310,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -5346,13 +5341,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473515</v>
+        <v>473680</v>
       </c>
       <c r="R34" t="n">
-        <v>7045852</v>
+        <v>7046060</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5386,7 +5381,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Enstaka bålar av lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5406,27 +5401,32 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, båhål (hackspettar) i grov asp, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5444,7 +5444,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121238149</v>
+        <v>121245697</v>
       </c>
       <c r="B35" t="n">
         <v>78609</v>
@@ -5483,14 +5483,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473540</v>
+        <v>473293</v>
       </c>
       <c r="R35" t="n">
-        <v>7046097</v>
+        <v>7045728</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5585,10 +5585,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121218973</v>
+        <v>121260476</v>
       </c>
       <c r="B36" t="n">
-        <v>90720</v>
+        <v>74707</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5601,21 +5601,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5628,13 +5628,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473506</v>
+        <v>473489</v>
       </c>
       <c r="R36" t="n">
-        <v>7046084</v>
+        <v>7046095</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5693,22 +5693,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Wood surface of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5726,10 +5726,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121260476</v>
+        <v>121218973</v>
       </c>
       <c r="B37" t="n">
-        <v>74707</v>
+        <v>90720</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5742,21 +5742,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5769,13 +5769,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473489</v>
+        <v>473506</v>
       </c>
       <c r="R37" t="n">
-        <v>7046095</v>
+        <v>7046084</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5834,22 +5834,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Betula</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>

--- a/artfynd/A 39937-2024 artfynd.xlsx
+++ b/artfynd/A 39937-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121219221</v>
+        <v>121244830</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473234</v>
+        <v>473247</v>
       </c>
       <c r="R2" t="n">
-        <v>7045879</v>
+        <v>7045894</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -767,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,7 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -799,14 +786,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -824,15 +816,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121219351</v>
+        <v>121245697</v>
       </c>
       <c r="B3" t="n">
-        <v>98105</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,54 +827,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473214</v>
+        <v>473293</v>
       </c>
       <c r="R3" t="n">
-        <v>7045971</v>
+        <v>7045728</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -924,7 +894,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -944,7 +914,27 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -962,15 +952,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121219485</v>
+        <v>121219221</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,20 +985,24 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473631</v>
+        <v>473234</v>
       </c>
       <c r="R4" t="n">
-        <v>7045992</v>
+        <v>7045879</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1050,7 +1039,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om färska ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1107,32 +1096,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121219127</v>
+        <v>121245253</v>
       </c>
       <c r="B5" t="n">
-        <v>98105</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>219811</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1142,7 +1126,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1152,7 +1136,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1167,10 +1151,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473560</v>
+        <v>473295</v>
       </c>
       <c r="R5" t="n">
-        <v>7046115</v>
+        <v>7045804</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1207,7 +1191,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Knärot med minst 33 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Minst 4 st vinterståndare av brudsporre. Obs! Fyndplatsen finns mycket nära en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1222,12 +1206,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Våtmark med gran</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Fuktig/blöt mark med gles trädställning av främst gran.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1245,57 +1229,65 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121247570</v>
+        <v>121219351</v>
       </c>
       <c r="B6" t="n">
-        <v>79691</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473680</v>
+        <v>473214</v>
       </c>
       <c r="R6" t="n">
-        <v>7046060</v>
+        <v>7045971</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1332,7 +1324,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Enstaka bålar av skrovellav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Knärot med minst 58 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1353,31 +1345,6 @@
       <c r="AI6" t="inlineStr">
         <is>
           <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1395,15 +1362,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121238149</v>
+        <v>121260476</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,21 +1373,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1434,17 +1396,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473540</v>
+        <v>473489</v>
       </c>
       <c r="R7" t="n">
-        <v>7046097</v>
+        <v>7046095</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1478,7 +1440,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1503,22 +1465,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Wood surface of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1536,15 +1498,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121231824</v>
+        <v>121218973</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1552,21 +1509,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1579,10 +1536,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473642</v>
+        <v>473506</v>
       </c>
       <c r="R8" t="n">
-        <v>7046059</v>
+        <v>7046084</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1619,7 +1576,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1654,12 +1611,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1677,15 +1634,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121244830</v>
+        <v>121246432</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1693,26 +1645,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1720,10 +1676,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473247</v>
+        <v>473702</v>
       </c>
       <c r="R9" t="n">
-        <v>7045894</v>
+        <v>7046035</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1760,7 +1716,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1780,32 +1736,32 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk- och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Flera granar.</t>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1823,15 +1779,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121231827</v>
+        <v>121247570</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1839,26 +1790,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1866,10 +1821,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473583</v>
+        <v>473680</v>
       </c>
       <c r="R10" t="n">
-        <v>7046084</v>
+        <v>7046060</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1906,7 +1861,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Enstaka bålar av skrovellav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1931,22 +1886,27 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1964,37 +1924,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121241817</v>
+        <v>121238339</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -2003,14 +1958,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473522</v>
+        <v>473540</v>
       </c>
       <c r="R11" t="n">
-        <v>7045984</v>
+        <v>7046097</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2045,11 +2000,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -2067,7 +2017,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2082,12 +2032,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2105,37 +2055,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121246773</v>
+        <v>121231824</v>
       </c>
       <c r="B12" t="n">
-        <v>79690</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2148,10 +2093,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473688</v>
+        <v>473642</v>
       </c>
       <c r="R12" t="n">
-        <v>7046072</v>
+        <v>7046059</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2188,7 +2133,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Enstaka stora bålar av lunglav några meter upp på en grovbarkad sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2213,22 +2158,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2246,37 +2191,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121238339</v>
+        <v>121231827</v>
       </c>
       <c r="B13" t="n">
-        <v>91403</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2285,14 +2225,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473540</v>
+        <v>473583</v>
       </c>
       <c r="R13" t="n">
-        <v>7046097</v>
+        <v>7046084</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2327,6 +2267,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2359,12 +2304,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2385,16 +2330,11 @@
         <v>121231830</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2523,37 +2463,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121246191</v>
+        <v>121238149</v>
       </c>
       <c r="B15" t="n">
-        <v>78345</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2562,17 +2497,17 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473595</v>
+        <v>473540</v>
       </c>
       <c r="R15" t="n">
-        <v>7046005</v>
+        <v>7046097</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2606,7 +2541,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2626,27 +2561,27 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2664,69 +2599,51 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121244747</v>
+        <v>121241817</v>
       </c>
       <c r="B16" t="n">
-        <v>56560</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473482</v>
+        <v>473522</v>
       </c>
       <c r="R16" t="n">
-        <v>7045969</v>
+        <v>7045984</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2760,7 +2677,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2769,6 +2686,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2779,7 +2697,27 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2797,46 +2735,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121240324</v>
+        <v>121244154</v>
       </c>
       <c r="B17" t="n">
-        <v>79726</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2844,10 +2773,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473527</v>
+        <v>473456</v>
       </c>
       <c r="R17" t="n">
-        <v>7046057</v>
+        <v>7045981</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2882,6 +2811,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2899,32 +2833,27 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2942,15 +2871,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121242466</v>
+        <v>121241506</v>
       </c>
       <c r="B18" t="n">
-        <v>90738</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2958,38 +2882,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2997,10 +2909,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473518</v>
+        <v>473522</v>
       </c>
       <c r="R18" t="n">
-        <v>7045959</v>
+        <v>7045984</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3037,7 +2949,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om kolflarnlav på en kolad tallhögstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3057,32 +2969,32 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. På fyndplatsen är det särskilt gott om klenvuxna träd. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>En smal död gran som är knäckt vid basen.</t>
+          <t>En ca 4 meter hög högstubbe.</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies # En smal död gran som är knäckt vid basen.</t>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris # En ca 4 meter hög högstubbe.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3100,15 +3012,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121245981</v>
+        <v>121246191</v>
       </c>
       <c r="B19" t="n">
-        <v>90738</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3116,30 +3023,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3147,10 +3050,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473515</v>
+        <v>473595</v>
       </c>
       <c r="R19" t="n">
-        <v>7045852</v>
+        <v>7046005</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3187,7 +3090,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Kolflarnlav på en kolad tallstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3207,27 +3110,27 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, båhål (hackspettar) i grov asp, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Även med markkontakt. # Picea abies</t>
+          <t>Fire killed tree # Kolad ved. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3245,15 +3148,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121241506</v>
+        <v>121238543</v>
       </c>
       <c r="B20" t="n">
-        <v>78345</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3261,26 +3159,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3288,10 +3190,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473522</v>
+        <v>473527</v>
       </c>
       <c r="R20" t="n">
-        <v>7045984</v>
+        <v>7046057</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3328,7 +3230,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Gott om kolflarnlav på en kolad tallhögstubbe. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Fina exemplar av lunglav på en gammal sälg där vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3348,32 +3250,32 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>En ca 4 meter hög högstubbe.</t>
+          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Fire killed tree # Kolad ved. # Pinus sylvestris # En ca 4 meter hög högstubbe.</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3391,15 +3293,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121246207</v>
+        <v>121241235</v>
       </c>
       <c r="B21" t="n">
-        <v>90738</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3407,34 +3304,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3442,13 +3335,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473595</v>
+        <v>473521</v>
       </c>
       <c r="R21" t="n">
-        <v>7046005</v>
+        <v>7046016</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3482,7 +3375,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Minst 8 st fruktkroppar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3502,27 +3395,32 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # En upplyft lutande stam av en knäckt gran. # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3540,15 +3438,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121245877</v>
+        <v>121246773</v>
       </c>
       <c r="B22" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3556,46 +3449,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473507</v>
+        <v>473688</v>
       </c>
       <c r="R22" t="n">
-        <v>7045849</v>
+        <v>7046072</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3632,7 +3516,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Enstaka stora bålar av lunglav några meter upp på en grovbarkad sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3641,6 +3525,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3651,27 +3536,27 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3689,57 +3574,52 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121238387</v>
+        <v>121247565</v>
       </c>
       <c r="B23" t="n">
-        <v>79719</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473540</v>
+        <v>473680</v>
       </c>
       <c r="R23" t="n">
-        <v>7046097</v>
+        <v>7046060</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3774,6 +3654,11 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Enstaka bålar av lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3804,14 +3689,19 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
+        </is>
+      </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3829,15 +3719,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121246631</v>
+        <v>121238387</v>
       </c>
       <c r="B24" t="n">
-        <v>79719</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3872,14 +3757,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473702</v>
+        <v>473540</v>
       </c>
       <c r="R24" t="n">
-        <v>7046035</v>
+        <v>7046097</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3944,11 +3829,6 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>En flerstammig sälg.</t>
-        </is>
-      </c>
       <c r="AM24" t="inlineStr">
         <is>
           <t>Bark på levande träd</t>
@@ -3956,7 +3836,7 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3974,15 +3854,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121241286</v>
+        <v>121241304</v>
       </c>
       <c r="B25" t="n">
-        <v>79726</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3990,21 +3865,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -4119,15 +3994,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121247541</v>
+        <v>121246631</v>
       </c>
       <c r="B26" t="n">
-        <v>79726</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4135,21 +4005,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -4166,10 +4036,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473680</v>
+        <v>473702</v>
       </c>
       <c r="R26" t="n">
-        <v>7046060</v>
+        <v>7046035</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4236,17 +4106,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>En grov sälglåga.</t>
+          <t>En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4267,12 +4137,7 @@
         <v>121246722</v>
       </c>
       <c r="B27" t="n">
-        <v>79725</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4409,44 +4274,39 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121246432</v>
+        <v>121240324</v>
       </c>
       <c r="B28" t="n">
-        <v>79691</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4456,10 +4316,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473702</v>
+        <v>473527</v>
       </c>
       <c r="R28" t="n">
-        <v>7046035</v>
+        <v>7046057</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4494,11 +4354,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Skrovellav på en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4531,7 +4386,7 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>En flerstammig sälg.</t>
+          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
@@ -4541,7 +4396,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En flerstammig sälg.</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4559,37 +4414,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121238543</v>
+        <v>121241286</v>
       </c>
       <c r="B29" t="n">
-        <v>79690</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4606,10 +4456,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473527</v>
+        <v>473521</v>
       </c>
       <c r="R29" t="n">
-        <v>7046057</v>
+        <v>7046016</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4644,11 +4494,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Fina exemplar av lunglav på en gammal sälg där vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4681,17 +4526,17 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4709,42 +4554,41 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121244154</v>
+        <v>121247541</v>
       </c>
       <c r="B30" t="n">
-        <v>78609</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4752,10 +4596,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473456</v>
+        <v>473680</v>
       </c>
       <c r="R30" t="n">
-        <v>7045981</v>
+        <v>7046060</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4790,11 +4634,6 @@
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4812,27 +4651,32 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>En grov sälglåga.</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4850,32 +4694,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121238082</v>
+        <v>121245877</v>
       </c>
       <c r="B31" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4888,7 +4727,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4898,14 +4737,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
+          <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473540</v>
+        <v>473507</v>
       </c>
       <c r="R31" t="n">
-        <v>7046097</v>
+        <v>7045849</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4942,7 +4781,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Hackspår sannolikt skapade inom som längst 5 år tillbaks. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4961,7 +4800,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk mark.</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4981,7 +4820,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Även hackspår i en grov tallhögstubbe intill. # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4999,15 +4838,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121241235</v>
+        <v>121219485</v>
       </c>
       <c r="B32" t="n">
-        <v>79690</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5015,41 +4849,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473521</v>
+        <v>473631</v>
       </c>
       <c r="R32" t="n">
-        <v>7046016</v>
+        <v>7045992</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -5086,7 +4921,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gott om lunglav på en grov sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Äldre ringhack på en levande gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5095,7 +4930,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -5111,27 +4945,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5149,57 +4978,57 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121241304</v>
+        <v>121238082</v>
       </c>
       <c r="B33" t="n">
-        <v>79719</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473521</v>
+        <v>473540</v>
       </c>
       <c r="R33" t="n">
-        <v>7046016</v>
+        <v>7046097</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5234,13 +5063,17 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -5256,27 +5089,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5294,60 +5122,64 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121247565</v>
+        <v>121244747</v>
       </c>
       <c r="B34" t="n">
-        <v>79690</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gammalbodarna, Jmt</t>
+          <t>Gammalbodarna, Lars-Ersbodtjärnarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473680</v>
+        <v>473482</v>
       </c>
       <c r="R34" t="n">
-        <v>7046060</v>
+        <v>7045969</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5381,7 +5213,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5390,7 +5222,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5401,32 +5232,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>En grov sälglåga.</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea # En grov sälglåga.</t>
+          <t>Äldre grandominerad, flerskiktad skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk-fuktig och frisk mark.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5444,53 +5250,65 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121245697</v>
+        <v>121219127</v>
       </c>
       <c r="B35" t="n">
-        <v>78609</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473293</v>
+        <v>473560</v>
       </c>
       <c r="R35" t="n">
-        <v>7045728</v>
+        <v>7046115</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5527,7 +5345,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
+          <t>Knärot med minst 33 st skott/stjälkar och 3 st fröställningar inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5547,27 +5365,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, kolade stuppar som visar på tidigare brand, träd med socklar och gott om aktiva myrstackar. På frisk och fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5582,288 +5380,6 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>121260476</v>
-      </c>
-      <c r="B36" t="n">
-        <v>74707</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>308</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Brunpudrad nållav</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Chaenotheca gracillima</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Gammalbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>473489</v>
-      </c>
-      <c r="R36" t="n">
-        <v>7046095</v>
-      </c>
-      <c r="S36" t="n">
-        <v>10</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Aspås</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Betula</t>
-        </is>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>121218973</v>
-      </c>
-      <c r="B37" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Gammalbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>473506</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7046084</v>
-      </c>
-      <c r="S37" t="n">
-        <v>5</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Aspås</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 39937-2024.</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad, flerskiktad och luckig skog med olikåldriga träd och måttliga mängder död ved. Här finns spår av hackspettar, träd med socklar och gott om aktiva myrstackar. På frisk och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39937-2024 artfynd.xlsx
+++ b/artfynd/A 39937-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -808,6 +813,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121260476</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -944,6 +954,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121218973</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1089,6 +1104,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121246432</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1234,6 +1254,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121247570</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1365,6 +1390,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121238339</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1501,6 +1531,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231824</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1637,6 +1672,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231827</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1773,6 +1813,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231830</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1909,6 +1954,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121238149</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2045,6 +2095,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121241817</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2181,6 +2236,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121244154</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2322,6 +2382,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121244830</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2458,6 +2523,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121245697</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2599,6 +2669,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121241506</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2735,6 +2810,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121246191</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2880,6 +2960,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121238543</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3025,6 +3110,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121241235</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3161,6 +3251,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121246773</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3306,6 +3401,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121247565</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3441,6 +3541,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121238387</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3581,6 +3686,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121241304</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3721,6 +3831,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121246631</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3861,6 +3976,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121246722</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4001,6 +4121,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121240324</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4141,6 +4266,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121241286</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4281,6 +4411,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121247541</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4425,6 +4560,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121245877</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4569,6 +4709,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121219221</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4709,6 +4854,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121219485</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4853,6 +5003,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121238082</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4981,6 +5136,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121244747</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5114,6 +5274,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121245253</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5247,6 +5412,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121219127</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5380,8 +5550,49 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121219351</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>